--- a/data/trending_integrated_20261007_14.xlsx
+++ b/data/trending_integrated_20261007_14.xlsx
@@ -584,7 +584,7 @@
         <v>48</v>
       </c>
       <c r="G2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H2" t="n">
         <v>3.27</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26373989854</v>
+        <v>26378650214</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8240</v>
+        <v>7980</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.07%</t>
+          <t>'+18.22%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" t="n">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="H3" t="n">
         <v>5.12</v>
@@ -702,7 +702,7 @@
         <v>5.14</v>
       </c>
       <c r="O3" t="n">
-        <v>119669776260</v>
+        <v>127722081625</v>
       </c>
       <c r="P3" t="n">
         <v>23500</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부 규제 완화 및 용적률 상향 관련 뉴스. 성수동 재개발 기대감과 함께 급등.</t>
+          <t>정부의 용적률 상향 및 그린벨트 해제 발표에 따른 개발 기대감. 성수동 삼표타워 관련 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['용적률', '그린벨트', '재개발']</t>
+          <t>['용적률', '그린벨트', '성수동']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2810</v>
+        <v>2805</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.33%</t>
+          <t>'+17.12%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G4" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="H4" t="n">
         <v>1.36</v>
@@ -794,7 +794,7 @@
         <v>1.31</v>
       </c>
       <c r="O4" t="n">
-        <v>38438010640</v>
+        <v>39319941539</v>
       </c>
       <c r="P4" t="n">
         <v>6000</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2705</v>
+        <v>17070</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.42%</t>
+          <t>'+14.79%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.29</v>
+        <v>0.98</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>192</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="G5" t="n">
-        <v>82</v>
+        <v>324</v>
       </c>
       <c r="H5" t="n">
-        <v>0.82</v>
+        <v>2.37</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2385</v>
+        <v>14870</v>
       </c>
       <c r="K5" t="n">
-        <v>2510</v>
+        <v>15480</v>
       </c>
       <c r="L5" t="n">
-        <v>2900</v>
+        <v>17590</v>
       </c>
       <c r="M5" t="n">
-        <v>2505</v>
+        <v>14600</v>
       </c>
       <c r="N5" t="n">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>13675899295</v>
+        <v>281025635890</v>
       </c>
       <c r="P5" t="n">
-        <v>4760</v>
+        <v>17590</v>
       </c>
       <c r="Q5" t="n">
-        <v>973</v>
+        <v>6320</v>
       </c>
       <c r="R5" t="n">
-        <v>5000</v>
+        <v>-94000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
+          <t>개인정보 유출 및 해킹 이슈 부각, 라온시큐어의 양자보안 기술 공급 논의 및 수주 기대감 형성. 미국 보안주 강세 동반.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['바이오', '유상증자', '기술적 반등']</t>
+          <t>['양자보안', '개인정보 유출', '수주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,43 +919,43 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16720</v>
+        <v>2700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.44%</t>
+          <t>'+13.21%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.98</v>
+        <v>-0.29</v>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>323</v>
+        <v>85</v>
       </c>
       <c r="H6" t="n">
-        <v>2.37</v>
+        <v>0.82</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14870</v>
+        <v>2385</v>
       </c>
       <c r="K6" t="n">
-        <v>15480</v>
+        <v>2510</v>
       </c>
       <c r="L6" t="n">
-        <v>17590</v>
+        <v>2900</v>
       </c>
       <c r="M6" t="n">
-        <v>14600</v>
+        <v>2505</v>
       </c>
       <c r="N6" t="n">
-        <v>1.39</v>
+        <v>1.11</v>
       </c>
       <c r="O6" t="n">
-        <v>275693089460</v>
+        <v>14241169575</v>
       </c>
       <c r="P6" t="n">
-        <v>17590</v>
+        <v>4760</v>
       </c>
       <c r="Q6" t="n">
-        <v>6320</v>
+        <v>973</v>
       </c>
       <c r="R6" t="n">
-        <v>-94000</v>
+        <v>5000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>개인정보 유출 및 해킹 이슈 부각, 라온시큐어의 양자보안 기술 공급 논의 및 수주 기대감 형성. 미국 보안주 강세 동반.</t>
+          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['양자보안', '개인정보 유출', '수주']</t>
+          <t>['바이오', '유상증자', '기술적 반등']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,82 +1011,82 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25700</v>
+        <v>10850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+11.98%</t>
+          <t>'+12.20%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="E7" t="n">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="G7" t="n">
-        <v>259</v>
+        <v>384</v>
       </c>
       <c r="H7" t="n">
-        <v>2.82</v>
+        <v>5.01</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>22950</v>
+        <v>9670</v>
       </c>
       <c r="K7" t="n">
-        <v>26200</v>
+        <v>11020</v>
       </c>
       <c r="L7" t="n">
-        <v>27600</v>
+        <v>11030</v>
       </c>
       <c r="M7" t="n">
-        <v>25550</v>
+        <v>10300</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>4.84</v>
       </c>
       <c r="O7" t="n">
-        <v>99961431075</v>
+        <v>20996553825</v>
       </c>
       <c r="P7" t="n">
-        <v>30100</v>
+        <v>15900</v>
       </c>
       <c r="Q7" t="n">
-        <v>11140</v>
+        <v>6310</v>
       </c>
       <c r="R7" t="n">
-        <v>177000</v>
+        <v>-210000</v>
       </c>
       <c r="S7" t="n">
-        <v>-231000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>유리 기술력 기반 성장 기대감. 브로드컴, 씨게이트 등 대기업과의 협력 가능성.</t>
+          <t>페스트, 에볼라 등 전염병 확산 관련주로 주목받으며 기대감 형성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유리', '기술력', '협력']</t>
+          <t>['전염병', '테마주', '흑사병']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10710</v>
+        <v>25750</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+10.75%</t>
+          <t>'+12.20%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.17</v>
+        <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="F8" t="n">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>378</v>
+        <v>261</v>
       </c>
       <c r="H8" t="n">
-        <v>5.01</v>
+        <v>2.82</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9670</v>
+        <v>22950</v>
       </c>
       <c r="K8" t="n">
-        <v>11020</v>
+        <v>26200</v>
       </c>
       <c r="L8" t="n">
-        <v>11030</v>
+        <v>27600</v>
       </c>
       <c r="M8" t="n">
-        <v>10300</v>
+        <v>25550</v>
       </c>
       <c r="N8" t="n">
-        <v>4.84</v>
+        <v>2.42</v>
       </c>
       <c r="O8" t="n">
-        <v>20458506945</v>
+        <v>100471005325</v>
       </c>
       <c r="P8" t="n">
-        <v>15900</v>
+        <v>30100</v>
       </c>
       <c r="Q8" t="n">
-        <v>6310</v>
+        <v>11140</v>
       </c>
       <c r="R8" t="n">
-        <v>-210000</v>
+        <v>177000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-231000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>페스트, 에볼라 등 전염병 확산 관련주로 주목받으며 기대감 형성.</t>
+          <t>유리 기술력 기반 성장 기대감. 브로드컴, 씨게이트 등 대기업과의 협력 가능성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['전염병', '테마주', '흑사병']</t>
+          <t>['유리', '기술력', '협력']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>204270</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13090</v>
+        <v>13060</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+6.16%</t>
+          <t>'+5.92%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F9" t="n">
         <v>69</v>
       </c>
       <c r="G9" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H9" t="n">
         <v>0.79</v>
@@ -1254,7 +1254,7 @@
         <v>0.48</v>
       </c>
       <c r="O9" t="n">
-        <v>189399785300</v>
+        <v>192209497895</v>
       </c>
       <c r="P9" t="n">
         <v>20850</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5140</v>
+        <v>5100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.59%</t>
+          <t>'+1.80%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>3.32</v>
       </c>
       <c r="E10" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F10" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G10" t="n">
-        <v>424</v>
+        <v>443</v>
       </c>
       <c r="H10" t="n">
         <v>4.72</v>
@@ -1346,7 +1346,7 @@
         <v>1.4</v>
       </c>
       <c r="O10" t="n">
-        <v>230593468980</v>
+        <v>232314203765</v>
       </c>
       <c r="P10" t="n">
         <v>8100</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>해외 기술주 강세와 연동되는 흐름. 대규모 선주문 규모 확인 및 추가 상승 기대.</t>
+          <t>미국 시장 호조와 2200억 규모 선주문 소식 기반 상승 기대감. 매수 주체 관련 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['기술주', '선주문', '상승']</t>
+          <t>['선주문', '발주서', '미국 시장']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>242750</v>
+        <v>13220</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.73%</t>
+          <t>'+1.61%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.04</v>
+        <v>1.88</v>
       </c>
       <c r="E11" t="n">
-        <v>187</v>
+        <v>79</v>
       </c>
       <c r="F11" t="n">
-        <v>116</v>
+        <v>59</v>
       </c>
       <c r="G11" t="n">
-        <v>1060</v>
+        <v>225</v>
       </c>
       <c r="H11" t="n">
-        <v>4.12</v>
+        <v>1.42</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,143 +1423,143 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>241000</v>
+        <v>13010</v>
       </c>
       <c r="K11" t="n">
-        <v>253000</v>
+        <v>12330</v>
       </c>
       <c r="L11" t="n">
-        <v>257000</v>
+        <v>13560</v>
       </c>
       <c r="M11" t="n">
-        <v>233500</v>
+        <v>12220</v>
       </c>
       <c r="N11" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>90278284500</v>
+        <v>42728014135</v>
       </c>
       <c r="P11" t="n">
-        <v>1233000</v>
+        <v>22250</v>
       </c>
       <c r="Q11" t="n">
-        <v>120000</v>
+        <v>6000</v>
       </c>
       <c r="R11" t="n">
-        <v>-72000</v>
+        <v>-170000</v>
       </c>
       <c r="S11" t="n">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>삼천당제약의 아일리아 관련 상승세 및 향후 미래 전망 강조. 경구용 인슐린 L/O 기대감과 외국인 수급 변화 주목.</t>
+          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['아일리아', '경구용 인슐린', '외국인 수급']</t>
+          <t>['유증', '신주상장', '자사주매집']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>270750</v>
+        <v>244500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.46%</t>
+          <t>'+1.45%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>190</v>
       </c>
       <c r="F12" t="n">
-        <v>484</v>
+        <v>118</v>
       </c>
       <c r="G12" t="n">
-        <v>1406</v>
+        <v>1083</v>
       </c>
       <c r="H12" t="n">
-        <v>46.37</v>
+        <v>4.12</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>272000</v>
+        <v>241000</v>
       </c>
       <c r="K12" t="n">
-        <v>269500</v>
+        <v>253000</v>
       </c>
       <c r="L12" t="n">
-        <v>279500</v>
+        <v>257000</v>
       </c>
       <c r="M12" t="n">
-        <v>268500</v>
+        <v>233500</v>
       </c>
       <c r="N12" t="n">
-        <v>46.41</v>
+        <v>4.08</v>
       </c>
       <c r="O12" t="n">
-        <v>3098788851500</v>
+        <v>91323596750</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>1233000</v>
       </c>
       <c r="Q12" t="n">
-        <v>90200</v>
+        <v>120000</v>
       </c>
       <c r="R12" t="n">
-        <v>1438000</v>
+        <v>-72000</v>
       </c>
       <c r="S12" t="n">
-        <v>-173000</v>
+        <v>2000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>외국인 및 기관 매도세 지속 속 정치적 이슈 언급. 삼전 실적 110조 이상 전망 제시.</t>
+          <t>삼천당제약의 아일리아 관련 상승세 및 향후 미래 전망 강조. 경구용 인슐린 L/O 기대감과 외국인 수급 변화 주목.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['실적', '매도세', '정치']</t>
+          <t>['아일리아', '경구용 인슐린', '외국인 수급']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>80700</v>
+        <v>270500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.98%</t>
+          <t>'-0.55%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>314</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>168</v>
+        <v>481</v>
       </c>
       <c r="G13" t="n">
-        <v>842</v>
+        <v>1413</v>
       </c>
       <c r="H13" t="n">
-        <v>22.59</v>
+        <v>46.37</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>81500</v>
+        <v>272000</v>
       </c>
       <c r="K13" t="n">
-        <v>83500</v>
+        <v>269500</v>
       </c>
       <c r="L13" t="n">
-        <v>84300</v>
+        <v>279500</v>
       </c>
       <c r="M13" t="n">
-        <v>80600</v>
+        <v>268500</v>
       </c>
       <c r="N13" t="n">
-        <v>22.56</v>
+        <v>46.41</v>
       </c>
       <c r="O13" t="n">
-        <v>140371161500</v>
+        <v>3242159450750</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>90200</v>
       </c>
       <c r="R13" t="n">
-        <v>-204000</v>
+        <v>1438000</v>
       </c>
       <c r="S13" t="n">
-        <v>-30000</v>
+        <v>-173000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 원전주 급등에 따른 기대감 형성. 구글과 컨스텔레이션 간 전력 구매 계약 체결 소식 및 웨스팅하우스 계약 공시 가능성 언급.</t>
+          <t>다수의 부정적 언급과 정치적 이슈 연관성에 따른 하락 전망. 삼전 실적 호조 가능성 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', '전력 구매 계약', '호재']</t>
+          <t>['실적', '매도', '리스크']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,169 +1660,169 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12830</v>
+        <v>80700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.38%</t>
+          <t>'-0.98%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.88</v>
+        <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>73</v>
+        <v>320</v>
       </c>
       <c r="F14" t="n">
-        <v>55</v>
+        <v>172</v>
       </c>
       <c r="G14" t="n">
-        <v>224</v>
+        <v>855</v>
       </c>
       <c r="H14" t="n">
-        <v>1.42</v>
+        <v>22.59</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>13010</v>
+        <v>81500</v>
       </c>
       <c r="K14" t="n">
-        <v>12330</v>
+        <v>83500</v>
       </c>
       <c r="L14" t="n">
-        <v>13560</v>
+        <v>84300</v>
       </c>
       <c r="M14" t="n">
-        <v>12220</v>
+        <v>80600</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>22.56</v>
       </c>
       <c r="O14" t="n">
-        <v>39339749950</v>
+        <v>142598354850</v>
       </c>
       <c r="P14" t="n">
-        <v>22250</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>6000</v>
+        <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>-170000</v>
+        <v>-204000</v>
       </c>
       <c r="S14" t="n">
-        <v>13000</v>
+        <v>-30000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
+          <t>구글과 미국 원전 기업의 전력 구매 계약 체결 소식 기반 상승 기대. 웨스팅하우스 계약 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['유증', '신주상장', '자사주매집']</t>
+          <t>['원전', '전력 구매 계약', '구글']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17480</v>
+        <v>6900</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.52%</t>
+          <t>'-1.15%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.11</v>
+        <v>-0.77</v>
       </c>
       <c r="E15" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G15" t="n">
-        <v>398</v>
+        <v>219</v>
       </c>
       <c r="H15" t="n">
-        <v>9.5</v>
+        <v>1.1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17750</v>
+        <v>6980</v>
       </c>
       <c r="K15" t="n">
-        <v>17970</v>
+        <v>7000</v>
       </c>
       <c r="L15" t="n">
-        <v>18030</v>
+        <v>7240</v>
       </c>
       <c r="M15" t="n">
-        <v>17420</v>
+        <v>6580</v>
       </c>
       <c r="N15" t="n">
-        <v>9.390000000000001</v>
+        <v>1.87</v>
       </c>
       <c r="O15" t="n">
-        <v>48842523550</v>
+        <v>67066456815</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>11370</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>3300</v>
       </c>
       <c r="R15" t="n">
-        <v>-193000</v>
+        <v>29000</v>
       </c>
       <c r="S15" t="n">
-        <v>-40000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 원전 건설 호재 및 수주 목표 달성 기대감. 주주 호소 및 긍정적 전망 다수.</t>
+          <t>보안주로 분류되며 금융권 공략 뉴스 부각. 라온시큐어와의 비교 언급 및 거래량 대비 주가 움직임에 대한 아쉬움 표출.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전', '수주', '주주']</t>
+          <t>['보안', '금융권']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6850</v>
+        <v>17480</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.86%</t>
+          <t>'-1.52%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.77</v>
+        <v>0.11</v>
       </c>
       <c r="E16" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="F16" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>225</v>
+        <v>404</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1</v>
+        <v>9.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6980</v>
+        <v>17750</v>
       </c>
       <c r="K16" t="n">
-        <v>7000</v>
+        <v>17970</v>
       </c>
       <c r="L16" t="n">
-        <v>7240</v>
+        <v>18030</v>
       </c>
       <c r="M16" t="n">
-        <v>6580</v>
+        <v>17420</v>
       </c>
       <c r="N16" t="n">
-        <v>1.87</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>66393076600</v>
+        <v>49674342540</v>
       </c>
       <c r="P16" t="n">
-        <v>11370</v>
+        <v>40350</v>
       </c>
       <c r="Q16" t="n">
-        <v>3300</v>
+        <v>3320</v>
       </c>
       <c r="R16" t="n">
-        <v>29000</v>
+        <v>-193000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-40000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>보안주로 분류되며 금융권 공략 뉴스 부각. 라온시큐어와의 비교 언급 및 거래량 대비 주가 움직임에 대한 아쉬움 표출.</t>
+          <t>미국 원전 건설 호재 및 수주 목표 달성 기대감. 주주 호소 및 긍정적 전망 다수.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['보안', '금융권']</t>
+          <t>['원전', '수주', '주주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13110</v>
+        <v>13105</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.09%</t>
+          <t>'-2.13%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1990,7 +1990,7 @@
         <v>3.12</v>
       </c>
       <c r="O17" t="n">
-        <v>26033363635</v>
+        <v>26262397810</v>
       </c>
       <c r="P17" t="n">
         <v>20300</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1733000</v>
+        <v>1730000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.26%</t>
+          <t>'-2.43%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="G18" t="n">
-        <v>1897</v>
+        <v>1949</v>
       </c>
       <c r="H18" t="n">
         <v>49.71</v>
@@ -2082,7 +2082,7 @@
         <v>49.76</v>
       </c>
       <c r="O18" t="n">
-        <v>3139757155000</v>
+        <v>3235912000500</v>
       </c>
       <c r="P18" t="n">
         <v>2987000</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>외국인 매도세 지속 및 추세선 하향 이탈에 대한 우려. 정치적 이슈와 공매도 관련 불만 제기.</t>
+          <t>외인 매도세와 정치적 이슈 연관성에 따른 하락 우려. 키옥시아 사례 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>46025</v>
+        <v>46200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.90%</t>
+          <t>'-2.53%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="F19" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>2326</v>
+        <v>2314</v>
       </c>
       <c r="H19" t="n">
         <v>14.12</v>
@@ -2174,7 +2174,7 @@
         <v>14.1</v>
       </c>
       <c r="O19" t="n">
-        <v>40424130250</v>
+        <v>41295235850</v>
       </c>
       <c r="P19" t="n">
         <v>69200</v>
@@ -2234,13 +2234,13 @@
         <v>1.11</v>
       </c>
       <c r="E20" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F20" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G20" t="n">
-        <v>1086</v>
+        <v>1100</v>
       </c>
       <c r="H20" t="n">
         <v>4.92</v>
@@ -2266,7 +2266,7 @@
         <v>3.81</v>
       </c>
       <c r="O20" t="n">
-        <v>276982246405</v>
+        <v>280482456265</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 강세 영향. 젠슨 황의 광통신 투자 언급.</t>
+          <t>광통신 업종의 미국 시장 강세 및 젠슨 황의 긍정적 전망 기반 상승 기대. 외인 매도세 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['광통신', '미국 주가', '젠슨 황']</t>
+          <t>['광통신', '젠슨 황', '미국 시장']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30150</v>
+        <v>30050</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.04%</t>
+          <t>'-5.35%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F21" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G21" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H21" t="n">
         <v>10.78</v>
@@ -2358,7 +2358,7 @@
         <v>10.77</v>
       </c>
       <c r="O21" t="n">
-        <v>95630384325</v>
+        <v>97497493425</v>
       </c>
       <c r="P21" t="n">
         <v>75900</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12600</v>
+        <v>12620</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.16%</t>
+          <t>'-8.02%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.43</v>
       </c>
       <c r="E22" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F22" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G22" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H22" t="n">
         <v>2.04</v>
@@ -2450,7 +2450,7 @@
         <v>2.47</v>
       </c>
       <c r="O22" t="n">
-        <v>58208019615</v>
+        <v>58662713780</v>
       </c>
       <c r="P22" t="n">
         <v>39600</v>

--- a/data/trending_integrated_20261007_14.xlsx
+++ b/data/trending_integrated_20261007_14.xlsx
@@ -578,10 +578,10 @@
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
         <v>51</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26378650214</v>
+        <v>26383195394</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>국전</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7980</v>
+        <v>2855</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.22%</t>
+          <t>'+19.21%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>134</v>
+        <v>90</v>
       </c>
       <c r="F3" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="G3" t="n">
-        <v>481</v>
+        <v>99</v>
       </c>
       <c r="H3" t="n">
-        <v>5.12</v>
+        <v>1.36</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6750</v>
+        <v>2395</v>
       </c>
       <c r="K3" t="n">
-        <v>6710</v>
+        <v>2410</v>
       </c>
       <c r="L3" t="n">
-        <v>8450</v>
+        <v>3020</v>
       </c>
       <c r="M3" t="n">
-        <v>6690</v>
+        <v>2405</v>
       </c>
       <c r="N3" t="n">
-        <v>5.14</v>
+        <v>1.31</v>
       </c>
       <c r="O3" t="n">
-        <v>127722081625</v>
+        <v>39800175835</v>
       </c>
       <c r="P3" t="n">
-        <v>23500</v>
+        <v>6000</v>
       </c>
       <c r="Q3" t="n">
-        <v>2890</v>
+        <v>1700</v>
       </c>
       <c r="R3" t="n">
-        <v>-660000</v>
+        <v>-120000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부의 용적률 상향 및 그린벨트 해제 발표에 따른 개발 기대감. 성수동 삼표타워 관련 언급.</t>
+          <t>흑사병 테마 관련주로 언급되며 거래량은 터졌으나 큰 상승은 못함. 반도체/이차전지 소재 업체로 변신 시도 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['용적률', '그린벨트', '성수동']</t>
+          <t>['흑사병', '테마주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,82 +735,82 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>307750</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>국전</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2805</v>
+        <v>11210</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.12%</t>
+          <t>'+15.93%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
-        <v>98</v>
+        <v>388</v>
       </c>
       <c r="H4" t="n">
-        <v>1.36</v>
+        <v>5.01</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2395</v>
+        <v>9670</v>
       </c>
       <c r="K4" t="n">
-        <v>2410</v>
+        <v>11020</v>
       </c>
       <c r="L4" t="n">
-        <v>3020</v>
+        <v>11240</v>
       </c>
       <c r="M4" t="n">
-        <v>2405</v>
+        <v>10300</v>
       </c>
       <c r="N4" t="n">
-        <v>1.31</v>
+        <v>4.84</v>
       </c>
       <c r="O4" t="n">
-        <v>39319941539</v>
+        <v>24320363070</v>
       </c>
       <c r="P4" t="n">
-        <v>6000</v>
+        <v>15900</v>
       </c>
       <c r="Q4" t="n">
-        <v>1700</v>
+        <v>6310</v>
       </c>
       <c r="R4" t="n">
-        <v>-147000</v>
+        <v>-105000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>흑사병 테마 관련주로 언급되며 거래량은 터졌으나 큰 상승은 못함. 반도체/이차전지 소재 업체로 변신 시도 언급.</t>
+          <t>페스트, 에볼라 등 전염병 확산 관련주로 주목받으며 기대감 형성.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['흑사병', '테마주']</t>
+          <t>['전염병', '테마주', '흑사병']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>307750</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17070</v>
+        <v>7770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.79%</t>
+          <t>'+15.11%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.98</v>
+        <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>192</v>
+        <v>138</v>
       </c>
       <c r="F5" t="n">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="G5" t="n">
-        <v>324</v>
+        <v>475</v>
       </c>
       <c r="H5" t="n">
-        <v>2.37</v>
+        <v>5.12</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14870</v>
+        <v>6750</v>
       </c>
       <c r="K5" t="n">
-        <v>15480</v>
+        <v>6710</v>
       </c>
       <c r="L5" t="n">
-        <v>17590</v>
+        <v>8450</v>
       </c>
       <c r="M5" t="n">
-        <v>14600</v>
+        <v>6690</v>
       </c>
       <c r="N5" t="n">
-        <v>1.39</v>
+        <v>5.14</v>
       </c>
       <c r="O5" t="n">
-        <v>281025635890</v>
+        <v>134101063965</v>
       </c>
       <c r="P5" t="n">
-        <v>17590</v>
+        <v>23500</v>
       </c>
       <c r="Q5" t="n">
-        <v>6320</v>
+        <v>2890</v>
       </c>
       <c r="R5" t="n">
-        <v>-94000</v>
+        <v>-631000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>개인정보 유출 및 해킹 이슈 부각, 라온시큐어의 양자보안 기술 공급 논의 및 수주 기대감 형성. 미국 보안주 강세 동반.</t>
+          <t>정부의 용적률 상향 및 그린벨트 해제 관련 뉴스 언급. 10만원 목표가 제시 및 상승 추세 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['양자보안', '개인정보 유출', '수주']</t>
+          <t>['용적률', '그린벨트', '상승추세']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2700</v>
+        <v>16890</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+13.21%</t>
+          <t>'+13.58%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.29</v>
+        <v>0.98</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>186</v>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="G6" t="n">
-        <v>85</v>
+        <v>322</v>
       </c>
       <c r="H6" t="n">
-        <v>0.82</v>
+        <v>2.37</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2385</v>
+        <v>14870</v>
       </c>
       <c r="K6" t="n">
-        <v>2510</v>
+        <v>15480</v>
       </c>
       <c r="L6" t="n">
-        <v>2900</v>
+        <v>17590</v>
       </c>
       <c r="M6" t="n">
-        <v>2505</v>
+        <v>14600</v>
       </c>
       <c r="N6" t="n">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="O6" t="n">
-        <v>14241169575</v>
+        <v>284273469100</v>
       </c>
       <c r="P6" t="n">
-        <v>4760</v>
+        <v>17590</v>
       </c>
       <c r="Q6" t="n">
-        <v>973</v>
+        <v>6320</v>
       </c>
       <c r="R6" t="n">
-        <v>5000</v>
+        <v>-95000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
+          <t>개인정보 유출 및 해킹 이슈 부각, 라온시큐어의 양자보안 기술 공급 논의 및 수주 기대감 형성. 미국 보안주 강세 동반.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['바이오', '유상증자', '기술적 반등']</t>
+          <t>['양자보안', '개인정보 유출', '수주']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,82 +1011,82 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10850</v>
+        <v>2695</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+12.20%</t>
+          <t>'+13.00%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.17</v>
+        <v>-0.29</v>
       </c>
       <c r="E7" t="n">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="F7" t="n">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>384</v>
+        <v>87</v>
       </c>
       <c r="H7" t="n">
-        <v>5.01</v>
+        <v>0.82</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9670</v>
+        <v>2385</v>
       </c>
       <c r="K7" t="n">
-        <v>11020</v>
+        <v>2510</v>
       </c>
       <c r="L7" t="n">
-        <v>11030</v>
+        <v>2900</v>
       </c>
       <c r="M7" t="n">
-        <v>10300</v>
+        <v>2505</v>
       </c>
       <c r="N7" t="n">
-        <v>4.84</v>
+        <v>1.11</v>
       </c>
       <c r="O7" t="n">
-        <v>20996553825</v>
+        <v>14482520990</v>
       </c>
       <c r="P7" t="n">
-        <v>15900</v>
+        <v>4760</v>
       </c>
       <c r="Q7" t="n">
-        <v>6310</v>
+        <v>973</v>
       </c>
       <c r="R7" t="n">
-        <v>-210000</v>
+        <v>45000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>페스트, 에볼라 등 전염병 확산 관련주로 주목받으며 기대감 형성.</t>
+          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['전염병', '테마주', '흑사병']</t>
+          <t>['바이오', '유상증자', '기술적 반등']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25750</v>
+        <v>25900</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+12.20%</t>
+          <t>'+12.85%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F8" t="n">
         <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H8" t="n">
         <v>2.82</v>
@@ -1162,7 +1162,7 @@
         <v>2.42</v>
       </c>
       <c r="O8" t="n">
-        <v>100471005325</v>
+        <v>100978586325</v>
       </c>
       <c r="P8" t="n">
         <v>30100</v>
@@ -1171,10 +1171,10 @@
         <v>11140</v>
       </c>
       <c r="R8" t="n">
-        <v>177000</v>
+        <v>160000</v>
       </c>
       <c r="S8" t="n">
-        <v>-231000</v>
+        <v>-227000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13060</v>
+        <v>13380</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.92%</t>
+          <t>'+8.52%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="H9" t="n">
         <v>0.79</v>
@@ -1254,7 +1254,7 @@
         <v>0.48</v>
       </c>
       <c r="O9" t="n">
-        <v>192209497895</v>
+        <v>194285413480</v>
       </c>
       <c r="P9" t="n">
         <v>20850</v>
@@ -1263,7 +1263,7 @@
         <v>4020</v>
       </c>
       <c r="R9" t="n">
-        <v>-83000</v>
+        <v>-68000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5100</v>
+        <v>245500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.80%</t>
+          <t>'+1.87%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3.32</v>
+        <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="F10" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G10" t="n">
-        <v>443</v>
+        <v>1143</v>
       </c>
       <c r="H10" t="n">
-        <v>4.72</v>
+        <v>4.12</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>5010</v>
+        <v>241000</v>
       </c>
       <c r="K10" t="n">
-        <v>5120</v>
+        <v>253000</v>
       </c>
       <c r="L10" t="n">
-        <v>5990</v>
+        <v>257000</v>
       </c>
       <c r="M10" t="n">
-        <v>4950</v>
+        <v>233500</v>
       </c>
       <c r="N10" t="n">
-        <v>1.4</v>
+        <v>4.08</v>
       </c>
       <c r="O10" t="n">
-        <v>232314203765</v>
+        <v>92914699750</v>
       </c>
       <c r="P10" t="n">
-        <v>8100</v>
+        <v>1233000</v>
       </c>
       <c r="Q10" t="n">
-        <v>592</v>
+        <v>120000</v>
       </c>
       <c r="R10" t="n">
-        <v>123000</v>
+        <v>-78000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 시장 호조와 2200억 규모 선주문 소식 기반 상승 기대감. 매수 주체 관련 언급.</t>
+          <t>아일리아, 경구용 인슐린 L/O 등 신규 계약 공시 및 릴레이 계약 기대감. 외국인 공매도 숏커버링 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['선주문', '발주서', '미국 시장']</t>
+          <t>['계약공시', '숏커버링', '미래']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13220</v>
+        <v>5090</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.61%</t>
+          <t>'+1.60%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.88</v>
+        <v>3.32</v>
       </c>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="F11" t="n">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="G11" t="n">
-        <v>225</v>
+        <v>463</v>
       </c>
       <c r="H11" t="n">
-        <v>1.42</v>
+        <v>4.72</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13010</v>
+        <v>5010</v>
       </c>
       <c r="K11" t="n">
-        <v>12330</v>
+        <v>5120</v>
       </c>
       <c r="L11" t="n">
-        <v>13560</v>
+        <v>5990</v>
       </c>
       <c r="M11" t="n">
-        <v>12220</v>
+        <v>4950</v>
       </c>
       <c r="N11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>234425710385</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8100</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>592</v>
+      </c>
+      <c r="R11" t="n">
+        <v>83000</v>
+      </c>
+      <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="O11" t="n">
-        <v>42728014135</v>
-      </c>
-      <c r="P11" t="n">
-        <v>22250</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6000</v>
-      </c>
-      <c r="R11" t="n">
-        <v>-170000</v>
-      </c>
-      <c r="S11" t="n">
-        <v>13000</v>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
+          <t>미국 증시 강세와 함께 6천원대 안착 및 2200억 규모 발주서 언급. 상승 기대감 표출.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['유증', '신주상장', '자사주매집']</t>
+          <t>['미국증시', '발주서', '상승']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,95 +1471,95 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>244500</v>
+        <v>271000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.45%</t>
+          <t>'-0.37%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>190</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>118</v>
+        <v>483</v>
       </c>
       <c r="G12" t="n">
-        <v>1083</v>
+        <v>1368</v>
       </c>
       <c r="H12" t="n">
-        <v>4.12</v>
+        <v>46.37</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>241000</v>
+        <v>272000</v>
       </c>
       <c r="K12" t="n">
-        <v>253000</v>
+        <v>269500</v>
       </c>
       <c r="L12" t="n">
-        <v>257000</v>
+        <v>279500</v>
       </c>
       <c r="M12" t="n">
-        <v>233500</v>
+        <v>268500</v>
       </c>
       <c r="N12" t="n">
-        <v>4.08</v>
+        <v>46.41</v>
       </c>
       <c r="O12" t="n">
-        <v>91323596750</v>
+        <v>3380651143000</v>
       </c>
       <c r="P12" t="n">
-        <v>1233000</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>120000</v>
+        <v>90200</v>
       </c>
       <c r="R12" t="n">
-        <v>-72000</v>
+        <v>1548000</v>
       </c>
       <c r="S12" t="n">
-        <v>2000</v>
+        <v>-319000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>삼천당제약의 아일리아 관련 상승세 및 향후 미래 전망 강조. 경구용 인슐린 L/O 기대감과 외국인 수급 변화 주목.</t>
+          <t>정치적 발언과 함께 외인/기관 매도세에 대한 불만 표출. 삼전 실적 110조 이상 기대 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['아일리아', '경구용 인슐린', '외국인 수급']</t>
+          <t>['실적', '매도세', '정치']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,99 +1568,99 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>270500</v>
+        <v>12930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.55%</t>
+          <t>'-0.61%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.04</v>
+        <v>1.88</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>86</v>
       </c>
       <c r="F13" t="n">
-        <v>481</v>
+        <v>63</v>
       </c>
       <c r="G13" t="n">
-        <v>1413</v>
+        <v>239</v>
       </c>
       <c r="H13" t="n">
-        <v>46.37</v>
+        <v>1.42</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>272000</v>
+        <v>13010</v>
       </c>
       <c r="K13" t="n">
-        <v>269500</v>
+        <v>12330</v>
       </c>
       <c r="L13" t="n">
-        <v>279500</v>
+        <v>13560</v>
       </c>
       <c r="M13" t="n">
-        <v>268500</v>
+        <v>12220</v>
       </c>
       <c r="N13" t="n">
-        <v>46.41</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3242159450750</v>
+        <v>47023152590</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>22250</v>
       </c>
       <c r="Q13" t="n">
-        <v>90200</v>
+        <v>6000</v>
       </c>
       <c r="R13" t="n">
-        <v>1438000</v>
+        <v>-152000</v>
       </c>
       <c r="S13" t="n">
-        <v>-173000</v>
+        <v>16000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>다수의 부정적 언급과 정치적 이슈 연관성에 따른 하락 전망. 삼전 실적 호조 가능성 언급.</t>
+          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['실적', '매도', '리스크']</t>
+          <t>['유증', '신주상장', '자사주매집']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>80700</v>
+        <v>80500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.98%</t>
+          <t>'-1.23%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F14" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G14" t="n">
-        <v>855</v>
+        <v>869</v>
       </c>
       <c r="H14" t="n">
         <v>22.59</v>
@@ -1708,13 +1708,13 @@
         <v>84300</v>
       </c>
       <c r="M14" t="n">
-        <v>80600</v>
+        <v>80200</v>
       </c>
       <c r="N14" t="n">
         <v>22.56</v>
       </c>
       <c r="O14" t="n">
-        <v>142598354850</v>
+        <v>152882916750</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1723,10 +1723,10 @@
         <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>-204000</v>
+        <v>-231000</v>
       </c>
       <c r="S14" t="n">
-        <v>-30000</v>
+        <v>-52000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1759,70 +1759,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6900</v>
+        <v>17470</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.15%</t>
+          <t>'-1.58%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.77</v>
+        <v>0.11</v>
       </c>
       <c r="E15" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F15" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>219</v>
+        <v>397</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1</v>
+        <v>9.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6980</v>
+        <v>17750</v>
       </c>
       <c r="K15" t="n">
-        <v>7000</v>
+        <v>17970</v>
       </c>
       <c r="L15" t="n">
-        <v>7240</v>
+        <v>18030</v>
       </c>
       <c r="M15" t="n">
-        <v>6580</v>
+        <v>17420</v>
       </c>
       <c r="N15" t="n">
-        <v>1.87</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>67066456815</v>
+        <v>52097552545</v>
       </c>
       <c r="P15" t="n">
-        <v>11370</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>3300</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>29000</v>
+        <v>-31000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-50000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>보안주로 분류되며 금융권 공략 뉴스 부각. 라온시큐어와의 비교 언급 및 거래량 대비 주가 움직임에 대한 아쉬움 표출.</t>
+          <t>미국 원전 건설 호재 및 수주 목표 달성 기대감. 주주 호소 및 긍정적 전망 다수.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['보안', '금융권']</t>
+          <t>['원전', '수주', '주주']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17480</v>
+        <v>6820</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.52%</t>
+          <t>'-2.29%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.11</v>
+        <v>-0.77</v>
       </c>
       <c r="E16" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G16" t="n">
-        <v>404</v>
+        <v>222</v>
       </c>
       <c r="H16" t="n">
-        <v>9.5</v>
+        <v>1.1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>17750</v>
+        <v>6980</v>
       </c>
       <c r="K16" t="n">
-        <v>17970</v>
+        <v>7000</v>
       </c>
       <c r="L16" t="n">
-        <v>18030</v>
+        <v>7240</v>
       </c>
       <c r="M16" t="n">
-        <v>17420</v>
+        <v>6580</v>
       </c>
       <c r="N16" t="n">
-        <v>9.390000000000001</v>
+        <v>1.87</v>
       </c>
       <c r="O16" t="n">
-        <v>49674342540</v>
+        <v>67626086915</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>11370</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>3300</v>
       </c>
       <c r="R16" t="n">
-        <v>-193000</v>
+        <v>20000</v>
       </c>
       <c r="S16" t="n">
-        <v>-40000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 원전 건설 호재 및 수주 목표 달성 기대감. 주주 호소 및 긍정적 전망 다수.</t>
+          <t>보안주로 분류되며 금융권 공략 뉴스 부각. 라온시큐어와의 비교 언급 및 거래량 대비 주가 움직임에 대한 아쉬움 표출.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', '수주', '주주']</t>
+          <t>['보안', '금융권']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13105</v>
+        <v>13080</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.13%</t>
+          <t>'-2.32%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1984,13 +1984,13 @@
         <v>13830</v>
       </c>
       <c r="M17" t="n">
-        <v>13080</v>
+        <v>13075</v>
       </c>
       <c r="N17" t="n">
         <v>3.12</v>
       </c>
       <c r="O17" t="n">
-        <v>26262397810</v>
+        <v>26491818320</v>
       </c>
       <c r="P17" t="n">
         <v>20300</v>
@@ -1999,7 +1999,7 @@
         <v>3020</v>
       </c>
       <c r="R17" t="n">
-        <v>-312000</v>
+        <v>-313000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1730000</v>
+        <v>1731000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.43%</t>
+          <t>'-2.37%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="G18" t="n">
-        <v>1949</v>
+        <v>1925</v>
       </c>
       <c r="H18" t="n">
         <v>49.71</v>
@@ -2082,7 +2082,7 @@
         <v>49.76</v>
       </c>
       <c r="O18" t="n">
-        <v>3235912000500</v>
+        <v>3375905005000</v>
       </c>
       <c r="P18" t="n">
         <v>2987000</v>
@@ -2091,14 +2091,14 @@
         <v>403000</v>
       </c>
       <c r="R18" t="n">
-        <v>-387000</v>
+        <v>-471000</v>
       </c>
       <c r="S18" t="n">
-        <v>-80000</v>
+        <v>-89000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>외인 매도세와 정치적 이슈 연관성에 따른 하락 우려. 키옥시아 사례 및 공매도 관련 언급.</t>
+          <t>정치적 요인 및 외인 매도세를 하락 원인으로 지목. 추세선 이탈 및 100만원 하회 가능성 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['외인 매도', '추세선', '공매도']</t>
+          <t>['외인매도', '추세선', '정치']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>46200</v>
+        <v>46000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.53%</t>
+          <t>'-2.95%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F19" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G19" t="n">
-        <v>2314</v>
+        <v>2326</v>
       </c>
       <c r="H19" t="n">
         <v>14.12</v>
@@ -2174,7 +2174,7 @@
         <v>14.1</v>
       </c>
       <c r="O19" t="n">
-        <v>41295235850</v>
+        <v>42619526650</v>
       </c>
       <c r="P19" t="n">
         <v>69200</v>
@@ -2183,10 +2183,10 @@
         <v>24150</v>
       </c>
       <c r="R19" t="n">
-        <v>-17000</v>
+        <v>-61000</v>
       </c>
       <c r="S19" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17950</v>
+        <v>17900</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.13%</t>
+          <t>'-3.40%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1.11</v>
       </c>
       <c r="E20" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F20" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G20" t="n">
-        <v>1100</v>
+        <v>1109</v>
       </c>
       <c r="H20" t="n">
         <v>4.92</v>
@@ -2260,13 +2260,13 @@
         <v>19870</v>
       </c>
       <c r="M20" t="n">
-        <v>17880</v>
+        <v>17855</v>
       </c>
       <c r="N20" t="n">
         <v>3.81</v>
       </c>
       <c r="O20" t="n">
-        <v>280482456265</v>
+        <v>282937293080</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2275,14 +2275,14 @@
         <v>1272</v>
       </c>
       <c r="R20" t="n">
-        <v>-435000</v>
+        <v>-479000</v>
       </c>
       <c r="S20" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>광통신 업종의 미국 시장 강세 및 젠슨 황의 긍정적 전망 기반 상승 기대. 외인 매도세 언급.</t>
+          <t>광통신 섹터의 강세와 함께 대한광통신에 대한 긍정적 전망 제시. 5만원 목표가 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['광통신', '젠슨 황', '미국 시장']</t>
+          <t>['광통신', '모멘텀', '목표가']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30050</v>
+        <v>30100</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.35%</t>
+          <t>'-5.20%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F21" t="n">
         <v>74</v>
       </c>
       <c r="G21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H21" t="n">
         <v>10.78</v>
@@ -2352,13 +2352,13 @@
         <v>32850</v>
       </c>
       <c r="M21" t="n">
-        <v>30050</v>
+        <v>30000</v>
       </c>
       <c r="N21" t="n">
         <v>10.77</v>
       </c>
       <c r="O21" t="n">
-        <v>97497493425</v>
+        <v>100235854075</v>
       </c>
       <c r="P21" t="n">
         <v>75900</v>
@@ -2367,23 +2367,23 @@
         <v>15960</v>
       </c>
       <c r="R21" t="n">
-        <v>-635000</v>
+        <v>-703000</v>
       </c>
       <c r="S21" t="n">
-        <v>-35000</v>
+        <v>-40000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>경쟁사 대비 부진한 주가 흐름과 기관/외인 매도 물량 출회. 하락 추세 지속.</t>
+          <t>가온전선과의 비교를 통해 부진한 주가 흐름 지적. 개인 투자자들의 매수와 외인/기관의 매도세 관찰.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['주가', '기관', '외인']</t>
+          <t>['주가', '매도세', '비교']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12620</v>
+        <v>12700</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.02%</t>
+          <t>'-7.43%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.43</v>
       </c>
       <c r="E22" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F22" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G22" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H22" t="n">
         <v>2.04</v>
@@ -2450,7 +2450,7 @@
         <v>2.47</v>
       </c>
       <c r="O22" t="n">
-        <v>58662713780</v>
+        <v>59184847160</v>
       </c>
       <c r="P22" t="n">
         <v>39600</v>
@@ -2459,7 +2459,7 @@
         <v>7300</v>
       </c>
       <c r="R22" t="n">
-        <v>-84000</v>
+        <v>-136000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>

--- a/data/trending_integrated_20261007_14.xlsx
+++ b/data/trending_integrated_20261007_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H2" t="n">
         <v>3.27</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26383195394</v>
+        <v>26384586414</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -659,18 +659,18 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2855</v>
+        <v>2770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.21%</t>
+          <t>'+15.66%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F3" t="n">
         <v>48</v>
@@ -702,7 +702,7 @@
         <v>1.31</v>
       </c>
       <c r="O3" t="n">
-        <v>39800175835</v>
+        <v>40094501576</v>
       </c>
       <c r="P3" t="n">
         <v>6000</v>
@@ -747,79 +747,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11210</v>
+        <v>7790</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.93%</t>
+          <t>'+15.41%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.17</v>
+        <v>-0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="F4" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G4" t="n">
-        <v>388</v>
+        <v>498</v>
       </c>
       <c r="H4" t="n">
-        <v>5.01</v>
+        <v>5.12</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9670</v>
+        <v>6750</v>
       </c>
       <c r="K4" t="n">
-        <v>11020</v>
+        <v>6710</v>
       </c>
       <c r="L4" t="n">
-        <v>11240</v>
+        <v>8450</v>
       </c>
       <c r="M4" t="n">
-        <v>10300</v>
+        <v>6690</v>
       </c>
       <c r="N4" t="n">
-        <v>4.84</v>
+        <v>5.14</v>
       </c>
       <c r="O4" t="n">
-        <v>24320363070</v>
+        <v>136728149070</v>
       </c>
       <c r="P4" t="n">
-        <v>15900</v>
+        <v>23500</v>
       </c>
       <c r="Q4" t="n">
-        <v>6310</v>
+        <v>2890</v>
       </c>
       <c r="R4" t="n">
-        <v>-105000</v>
+        <v>-631000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>페스트, 에볼라 등 전염병 확산 관련주로 주목받으며 기대감 형성.</t>
+          <t>정부의 용적률 상향 및 그린벨트 해제 발표와 함께 성수동 삼표타워 건설 시작. 만원 돌파 기대감 및 거래량 증가.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['전염병', '테마주', '흑사병']</t>
+          <t>['용적률', '그린벨트', '거래량']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,43 +827,43 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7770</v>
+        <v>16880</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.11%</t>
+          <t>'+13.52%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.02</v>
+        <v>0.98</v>
       </c>
       <c r="E5" t="n">
-        <v>138</v>
+        <v>188</v>
       </c>
       <c r="F5" t="n">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="G5" t="n">
-        <v>475</v>
+        <v>323</v>
       </c>
       <c r="H5" t="n">
-        <v>5.12</v>
+        <v>2.37</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6750</v>
+        <v>14870</v>
       </c>
       <c r="K5" t="n">
-        <v>6710</v>
+        <v>15480</v>
       </c>
       <c r="L5" t="n">
-        <v>8450</v>
+        <v>17590</v>
       </c>
       <c r="M5" t="n">
-        <v>6690</v>
+        <v>14600</v>
       </c>
       <c r="N5" t="n">
-        <v>5.14</v>
+        <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>134101063965</v>
+        <v>285792362275</v>
       </c>
       <c r="P5" t="n">
-        <v>23500</v>
+        <v>17590</v>
       </c>
       <c r="Q5" t="n">
-        <v>2890</v>
+        <v>6320</v>
       </c>
       <c r="R5" t="n">
-        <v>-631000</v>
+        <v>-95000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정부의 용적률 상향 및 그린벨트 해제 관련 뉴스 언급. 10만원 목표가 제시 및 상승 추세 기대.</t>
+          <t>개인정보 유출 및 해킹 이슈 부각, 라온시큐어의 양자보안 기술 공급 논의 및 수주 기대감 형성. 미국 보안주 강세 동반.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['용적률', '그린벨트', '상승추세']</t>
+          <t>['양자보안', '개인정보 유출', '수주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16890</v>
+        <v>25950</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+13.58%</t>
+          <t>'+13.07%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.98</v>
+        <v>0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>186</v>
+        <v>93</v>
       </c>
       <c r="F6" t="n">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>322</v>
+        <v>277</v>
       </c>
       <c r="H6" t="n">
-        <v>2.37</v>
+        <v>2.82</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14870</v>
+        <v>22950</v>
       </c>
       <c r="K6" t="n">
-        <v>15480</v>
+        <v>26200</v>
       </c>
       <c r="L6" t="n">
-        <v>17590</v>
+        <v>27600</v>
       </c>
       <c r="M6" t="n">
-        <v>14600</v>
+        <v>25550</v>
       </c>
       <c r="N6" t="n">
-        <v>1.39</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>284273469100</v>
+        <v>101634840800</v>
       </c>
       <c r="P6" t="n">
-        <v>17590</v>
+        <v>30100</v>
       </c>
       <c r="Q6" t="n">
-        <v>6320</v>
+        <v>11140</v>
       </c>
       <c r="R6" t="n">
-        <v>-95000</v>
+        <v>160000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-227000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>개인정보 유출 및 해킹 이슈 부각, 라온시큐어의 양자보안 기술 공급 논의 및 수주 기대감 형성. 미국 보안주 강세 동반.</t>
+          <t>유리 기술력 기반 성장 기대감. 브로드컴, 씨게이트 등 대기업과의 협력 가능성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['양자보안', '개인정보 유출', '수주']</t>
+          <t>['유리', '기술력', '협력']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,91 +1011,91 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>204270</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2695</v>
+        <v>10920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+13.00%</t>
+          <t>'+12.93%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.29</v>
+        <v>0.17</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="F7" t="n">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="G7" t="n">
-        <v>87</v>
+        <v>421</v>
       </c>
       <c r="H7" t="n">
-        <v>0.82</v>
+        <v>5.01</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2385</v>
+        <v>9670</v>
       </c>
       <c r="K7" t="n">
-        <v>2510</v>
+        <v>11020</v>
       </c>
       <c r="L7" t="n">
-        <v>2900</v>
+        <v>11240</v>
       </c>
       <c r="M7" t="n">
-        <v>2505</v>
+        <v>10300</v>
       </c>
       <c r="N7" t="n">
-        <v>1.11</v>
+        <v>4.84</v>
       </c>
       <c r="O7" t="n">
-        <v>14482520990</v>
+        <v>26030307820</v>
       </c>
       <c r="P7" t="n">
-        <v>4760</v>
+        <v>15900</v>
       </c>
       <c r="Q7" t="n">
-        <v>973</v>
+        <v>6310</v>
       </c>
       <c r="R7" t="n">
-        <v>45000</v>
+        <v>-105000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
+          <t>신풍제약, 흑사병 및 전염병 테마주 부각. 사망자 발생 뉴스 및 모건스탠리 언급. 상한가 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['바이오', '유상증자', '기술적 반등']</t>
+          <t>['테마주', '흑사병', '사망자']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,43 +1103,43 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25900</v>
+        <v>2665</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+12.85%</t>
+          <t>'+11.74%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4</v>
+        <v>-0.29</v>
       </c>
       <c r="E8" t="n">
+        <v>55</v>
+      </c>
+      <c r="F8" t="n">
+        <v>28</v>
+      </c>
+      <c r="G8" t="n">
         <v>88</v>
       </c>
-      <c r="F8" t="n">
-        <v>41</v>
-      </c>
-      <c r="G8" t="n">
-        <v>264</v>
-      </c>
       <c r="H8" t="n">
-        <v>2.82</v>
+        <v>0.82</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>22950</v>
+        <v>2385</v>
       </c>
       <c r="K8" t="n">
-        <v>26200</v>
+        <v>2510</v>
       </c>
       <c r="L8" t="n">
-        <v>27600</v>
+        <v>2900</v>
       </c>
       <c r="M8" t="n">
-        <v>25550</v>
+        <v>2505</v>
       </c>
       <c r="N8" t="n">
-        <v>2.42</v>
+        <v>1.11</v>
       </c>
       <c r="O8" t="n">
-        <v>100978586325</v>
+        <v>14690595190</v>
       </c>
       <c r="P8" t="n">
-        <v>30100</v>
+        <v>4760</v>
       </c>
       <c r="Q8" t="n">
-        <v>11140</v>
+        <v>973</v>
       </c>
       <c r="R8" t="n">
-        <v>160000</v>
+        <v>45000</v>
       </c>
       <c r="S8" t="n">
-        <v>-227000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>유리 기술력 기반 성장 기대감. 브로드컴, 씨게이트 등 대기업과의 협력 가능성.</t>
+          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['유리', '기술력', '협력']</t>
+          <t>['바이오', '유상증자', '기술적 반등']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13380</v>
+        <v>13690</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.52%</t>
+          <t>'+11.03%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="F9" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G9" t="n">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="H9" t="n">
         <v>0.79</v>
@@ -1254,7 +1254,7 @@
         <v>0.48</v>
       </c>
       <c r="O9" t="n">
-        <v>194285413480</v>
+        <v>206396871405</v>
       </c>
       <c r="P9" t="n">
         <v>20850</v>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>245500</v>
+        <v>5140</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.87%</t>
+          <t>'+2.59%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.04</v>
+        <v>3.32</v>
       </c>
       <c r="E10" t="n">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="F10" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G10" t="n">
-        <v>1143</v>
+        <v>490</v>
       </c>
       <c r="H10" t="n">
-        <v>4.12</v>
+        <v>4.72</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>241000</v>
+        <v>5010</v>
       </c>
       <c r="K10" t="n">
-        <v>253000</v>
+        <v>5120</v>
       </c>
       <c r="L10" t="n">
-        <v>257000</v>
+        <v>5990</v>
       </c>
       <c r="M10" t="n">
-        <v>233500</v>
+        <v>4950</v>
       </c>
       <c r="N10" t="n">
-        <v>4.08</v>
+        <v>1.4</v>
       </c>
       <c r="O10" t="n">
-        <v>92914699750</v>
+        <v>235936129505</v>
       </c>
       <c r="P10" t="n">
-        <v>1233000</v>
+        <v>8100</v>
       </c>
       <c r="Q10" t="n">
-        <v>120000</v>
+        <v>592</v>
       </c>
       <c r="R10" t="n">
-        <v>-78000</v>
+        <v>83000</v>
       </c>
       <c r="S10" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>아일리아, 경구용 인슐린 L/O 등 신규 계약 공시 및 릴레이 계약 기대감. 외국인 공매도 숏커버링 언급.</t>
+          <t>미국 증시 상승 및 엠바고 해제된 2200억 규모 선주문 발주서 기반 상승 기대감. 주포의 빌드업 가능성 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['계약공시', '숏커버링', '미래']</t>
+          <t>['미국증시', '선주문', '주포']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5090</v>
+        <v>246000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.60%</t>
+          <t>'+2.07%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3.32</v>
+        <v>0.04</v>
       </c>
       <c r="E11" t="n">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="F11" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G11" t="n">
-        <v>463</v>
+        <v>1175</v>
       </c>
       <c r="H11" t="n">
-        <v>4.72</v>
+        <v>4.12</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>5010</v>
+        <v>241000</v>
       </c>
       <c r="K11" t="n">
-        <v>5120</v>
+        <v>253000</v>
       </c>
       <c r="L11" t="n">
-        <v>5990</v>
+        <v>257000</v>
       </c>
       <c r="M11" t="n">
-        <v>4950</v>
+        <v>233500</v>
       </c>
       <c r="N11" t="n">
-        <v>1.4</v>
+        <v>4.08</v>
       </c>
       <c r="O11" t="n">
-        <v>234425710385</v>
+        <v>94050829250</v>
       </c>
       <c r="P11" t="n">
-        <v>8100</v>
+        <v>1233000</v>
       </c>
       <c r="Q11" t="n">
-        <v>592</v>
+        <v>120000</v>
       </c>
       <c r="R11" t="n">
-        <v>83000</v>
+        <v>-78000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 증시 강세와 함께 6천원대 안착 및 2200억 규모 발주서 언급. 상승 기대감 표출.</t>
+          <t>아일리아 및 경구용 인슐린 관련 기대감, 릴레이 계약 공시 예상. 외인 공매도 숏커버링 및 캐나다/독일/이탈리아 계약 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['미국증시', '발주서', '상승']</t>
+          <t>['아일리아', '경구용인슐린', '계약공시']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>271000</v>
+        <v>271250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.37%</t>
+          <t>'-0.28%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="G12" t="n">
-        <v>1368</v>
+        <v>1310</v>
       </c>
       <c r="H12" t="n">
         <v>46.37</v>
@@ -1530,7 +1530,7 @@
         <v>46.41</v>
       </c>
       <c r="O12" t="n">
-        <v>3380651143000</v>
+        <v>3487864522250</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 발언과 함께 외인/기관 매도세에 대한 불만 표출. 삼전 실적 110조 이상 기대 언급.</t>
+          <t>정치적 언급과 함께 외인/국군 매도세 언급. 실적 110조 이상 예상에도 불구하고 상승 여력 제한적 관망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12930</v>
+        <v>12890</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.61%</t>
+          <t>'-0.92%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>1.88</v>
       </c>
       <c r="E13" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F13" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G13" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H13" t="n">
         <v>1.42</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>47023152590</v>
+        <v>48063563280</v>
       </c>
       <c r="P13" t="n">
         <v>22250</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>80500</v>
+        <v>80700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.23%</t>
+          <t>'-0.98%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F14" t="n">
         <v>171</v>
       </c>
       <c r="G14" t="n">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="H14" t="n">
         <v>22.59</v>
@@ -1714,7 +1714,7 @@
         <v>22.56</v>
       </c>
       <c r="O14" t="n">
-        <v>152882916750</v>
+        <v>157851366700</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>구글과 미국 원전 기업의 전력 구매 계약 체결 소식 기반 상승 기대. 웨스팅하우스 계약 가능성 언급.</t>
+          <t>미국 원전주 급등 및 구글의 전력구매 계약 체결 관련 호재. 공매도 박살 기대감 및 상승 여력.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', '전력 구매 계약', '구글']</t>
+          <t>['원전주', '전력구매계약', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17470</v>
+        <v>17490</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.58%</t>
+          <t>'-1.46%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.11</v>
       </c>
       <c r="E15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G15" t="n">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="H15" t="n">
         <v>9.5</v>
@@ -1806,7 +1806,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>52097552545</v>
+        <v>53059059280</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6820</v>
+        <v>6850</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.29%</t>
+          <t>'-1.86%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1898,7 +1898,7 @@
         <v>1.87</v>
       </c>
       <c r="O16" t="n">
-        <v>67626086915</v>
+        <v>67986837510</v>
       </c>
       <c r="P16" t="n">
         <v>11370</v>
@@ -1984,13 +1984,13 @@
         <v>13830</v>
       </c>
       <c r="M17" t="n">
-        <v>13075</v>
+        <v>13070</v>
       </c>
       <c r="N17" t="n">
         <v>3.12</v>
       </c>
       <c r="O17" t="n">
-        <v>26491818320</v>
+        <v>26770698045</v>
       </c>
       <c r="P17" t="n">
         <v>20300</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1731000</v>
+        <v>1729000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.37%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G18" t="n">
-        <v>1925</v>
+        <v>1943</v>
       </c>
       <c r="H18" t="n">
         <v>49.71</v>
@@ -2082,7 +2082,7 @@
         <v>49.76</v>
       </c>
       <c r="O18" t="n">
-        <v>3375905005000</v>
+        <v>3483211659500</v>
       </c>
       <c r="P18" t="n">
         <v>2987000</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>정치적 요인 및 외인 매도세를 하락 원인으로 지목. 추세선 이탈 및 100만원 하회 가능성 언급.</t>
+          <t>정치적 이슈와 함께 나스닥 및 외인 매도세로 인한 하락세 지속. 추세선 하향 돌파 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['외인매도', '추세선', '정치']</t>
+          <t>['정치', '매도세', '추세선']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2142,13 +2142,13 @@
         <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F19" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G19" t="n">
-        <v>2326</v>
+        <v>2347</v>
       </c>
       <c r="H19" t="n">
         <v>14.12</v>
@@ -2174,7 +2174,7 @@
         <v>14.1</v>
       </c>
       <c r="O19" t="n">
-        <v>42619526650</v>
+        <v>42978287850</v>
       </c>
       <c r="P19" t="n">
         <v>69200</v>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17900</v>
+        <v>17980</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.40%</t>
+          <t>'-2.97%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>133</v>
       </c>
       <c r="G20" t="n">
-        <v>1109</v>
+        <v>1114</v>
       </c>
       <c r="H20" t="n">
         <v>4.92</v>
@@ -2266,7 +2266,7 @@
         <v>3.81</v>
       </c>
       <c r="O20" t="n">
-        <v>282937293080</v>
+        <v>283729352470</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30100</v>
+        <v>30150</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.20%</t>
+          <t>'-5.04%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F21" t="n">
         <v>74</v>
       </c>
       <c r="G21" t="n">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="H21" t="n">
         <v>10.78</v>
@@ -2358,7 +2358,7 @@
         <v>10.77</v>
       </c>
       <c r="O21" t="n">
-        <v>100235854075</v>
+        <v>101521691000</v>
       </c>
       <c r="P21" t="n">
         <v>75900</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>가온전선과의 비교를 통해 부진한 주가 흐름 지적. 개인 투자자들의 매수와 외인/기관의 매도세 관찰.</t>
+          <t>가온전선과 비교되며 실력 및 기술력 차이 부각. 개인 매수세와 외인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['주가', '매도세', '비교']</t>
+          <t>['비교', '매도세', '개인']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2418,13 +2418,13 @@
         <v>-0.43</v>
       </c>
       <c r="E22" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F22" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G22" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="H22" t="n">
         <v>2.04</v>
@@ -2450,7 +2450,7 @@
         <v>2.47</v>
       </c>
       <c r="O22" t="n">
-        <v>59184847160</v>
+        <v>59510499040</v>
       </c>
       <c r="P22" t="n">
         <v>39600</v>

--- a/data/trending_integrated_20261007_14.xlsx
+++ b/data/trending_integrated_20261007_14.xlsx
@@ -584,7 +584,7 @@
         <v>51</v>
       </c>
       <c r="G2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H2" t="n">
         <v>3.27</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26384586414</v>
+        <v>26384852214</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2770</v>
+        <v>2765</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.66%</t>
+          <t>'+15.45%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F3" t="n">
         <v>48</v>
       </c>
       <c r="G3" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H3" t="n">
         <v>1.36</v>
@@ -702,7 +702,7 @@
         <v>1.31</v>
       </c>
       <c r="O3" t="n">
-        <v>40094501576</v>
+        <v>40435415416</v>
       </c>
       <c r="P3" t="n">
         <v>6000</v>
@@ -747,79 +747,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7790</v>
+        <v>11080</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.41%</t>
+          <t>'+14.58%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.02</v>
+        <v>0.17</v>
       </c>
       <c r="E4" t="n">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="F4" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G4" t="n">
-        <v>498</v>
+        <v>446</v>
       </c>
       <c r="H4" t="n">
-        <v>5.12</v>
+        <v>5.01</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6750</v>
+        <v>9670</v>
       </c>
       <c r="K4" t="n">
-        <v>6710</v>
+        <v>11020</v>
       </c>
       <c r="L4" t="n">
-        <v>8450</v>
+        <v>11240</v>
       </c>
       <c r="M4" t="n">
-        <v>6690</v>
+        <v>10300</v>
       </c>
       <c r="N4" t="n">
-        <v>5.14</v>
+        <v>4.84</v>
       </c>
       <c r="O4" t="n">
-        <v>136728149070</v>
+        <v>27725474380</v>
       </c>
       <c r="P4" t="n">
-        <v>23500</v>
+        <v>15900</v>
       </c>
       <c r="Q4" t="n">
-        <v>2890</v>
+        <v>6310</v>
       </c>
       <c r="R4" t="n">
-        <v>-631000</v>
+        <v>-105000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부의 용적률 상향 및 그린벨트 해제 발표와 함께 성수동 삼표타워 건설 시작. 만원 돌파 기대감 및 거래량 증가.</t>
+          <t>러시아 흑사병·케냐 에볼라 발병 소식에 신풍제약 급등. 만능 테마주로서의 기대감 부각.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['용적률', '그린벨트', '거래량']</t>
+          <t>['흑사병', '에볼라', '테마주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16880</v>
+        <v>7730</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.52%</t>
+          <t>'+14.52%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.98</v>
+        <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="F5" t="n">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="G5" t="n">
-        <v>323</v>
+        <v>510</v>
       </c>
       <c r="H5" t="n">
-        <v>2.37</v>
+        <v>5.12</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14870</v>
+        <v>6750</v>
       </c>
       <c r="K5" t="n">
-        <v>15480</v>
+        <v>6710</v>
       </c>
       <c r="L5" t="n">
-        <v>17590</v>
+        <v>8450</v>
       </c>
       <c r="M5" t="n">
-        <v>14600</v>
+        <v>6690</v>
       </c>
       <c r="N5" t="n">
-        <v>1.39</v>
+        <v>5.14</v>
       </c>
       <c r="O5" t="n">
-        <v>285792362275</v>
+        <v>138229200460</v>
       </c>
       <c r="P5" t="n">
-        <v>17590</v>
+        <v>23500</v>
       </c>
       <c r="Q5" t="n">
-        <v>6320</v>
+        <v>2890</v>
       </c>
       <c r="R5" t="n">
-        <v>-95000</v>
+        <v>-631000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>개인정보 유출 및 해킹 이슈 부각, 라온시큐어의 양자보안 기술 공급 논의 및 수주 기대감 형성. 미국 보안주 강세 동반.</t>
+          <t>정부의 용적률 상향 및 그린벨트 해제 발표와 함께 성수동 삼표타워 건설 시작. 만원 돌파 기대감 및 거래량 증가.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['양자보안', '개인정보 유출', '수주']</t>
+          <t>['용적률', '그린벨트', '거래량']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25950</v>
+        <v>16820</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+13.07%</t>
+          <t>'+13.11%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>0.98</v>
       </c>
       <c r="E6" t="n">
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="G6" t="n">
-        <v>277</v>
+        <v>335</v>
       </c>
       <c r="H6" t="n">
-        <v>2.82</v>
+        <v>2.37</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>22950</v>
+        <v>14870</v>
       </c>
       <c r="K6" t="n">
-        <v>26200</v>
+        <v>15480</v>
       </c>
       <c r="L6" t="n">
-        <v>27600</v>
+        <v>17590</v>
       </c>
       <c r="M6" t="n">
-        <v>25550</v>
+        <v>14600</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>1.39</v>
       </c>
       <c r="O6" t="n">
-        <v>101634840800</v>
+        <v>287351802440</v>
       </c>
       <c r="P6" t="n">
-        <v>30100</v>
+        <v>17590</v>
       </c>
       <c r="Q6" t="n">
-        <v>11140</v>
+        <v>6320</v>
       </c>
       <c r="R6" t="n">
-        <v>160000</v>
+        <v>-95000</v>
       </c>
       <c r="S6" t="n">
-        <v>-227000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>유리 기술력 기반 성장 기대감. 브로드컴, 씨게이트 등 대기업과의 협력 가능성.</t>
+          <t>국내외 해킹·보안 이슈 부각 속 라온시큐어 상승. 농협·KDB생명 해킹 방어 및 양자보안 공급 논의.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유리', '기술력', '협력']</t>
+          <t>['양자보안', '해킹', '보안주']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,91 +1011,91 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10920</v>
+        <v>25950</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+12.93%</t>
+          <t>'+13.07%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.17</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="F7" t="n">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>421</v>
+        <v>288</v>
       </c>
       <c r="H7" t="n">
-        <v>5.01</v>
+        <v>2.82</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9670</v>
+        <v>22950</v>
       </c>
       <c r="K7" t="n">
-        <v>11020</v>
+        <v>26200</v>
       </c>
       <c r="L7" t="n">
-        <v>11240</v>
+        <v>27600</v>
       </c>
       <c r="M7" t="n">
-        <v>10300</v>
+        <v>25550</v>
       </c>
       <c r="N7" t="n">
-        <v>4.84</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
-        <v>26030307820</v>
+        <v>102310983300</v>
       </c>
       <c r="P7" t="n">
-        <v>15900</v>
+        <v>30100</v>
       </c>
       <c r="Q7" t="n">
-        <v>6310</v>
+        <v>11140</v>
       </c>
       <c r="R7" t="n">
-        <v>-105000</v>
+        <v>160000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-227000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>신풍제약, 흑사병 및 전염병 테마주 부각. 사망자 발생 뉴스 및 모건스탠리 언급. 상한가 기대감.</t>
+          <t>유리 기술력 기반 성장 기대감. 브로드컴, 씨게이트 등 대기업과의 협력 가능성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['테마주', '흑사병', '사망자']</t>
+          <t>['유리', '기술력', '협력']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>204270</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2665</v>
+        <v>2635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+11.74%</t>
+          <t>'+10.48%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.29</v>
       </c>
       <c r="E8" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H8" t="n">
         <v>0.82</v>
@@ -1162,7 +1162,7 @@
         <v>1.11</v>
       </c>
       <c r="O8" t="n">
-        <v>14690595190</v>
+        <v>14986116415</v>
       </c>
       <c r="P8" t="n">
         <v>4760</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13690</v>
+        <v>13620</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+11.03%</t>
+          <t>'+10.46%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F9" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G9" t="n">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="H9" t="n">
         <v>0.79</v>
@@ -1254,7 +1254,7 @@
         <v>0.48</v>
       </c>
       <c r="O9" t="n">
-        <v>206396871405</v>
+        <v>214458798545</v>
       </c>
       <c r="P9" t="n">
         <v>20850</v>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5140</v>
+        <v>248500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.59%</t>
+          <t>'+3.11%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3.32</v>
+        <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="F10" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G10" t="n">
-        <v>490</v>
+        <v>1188</v>
       </c>
       <c r="H10" t="n">
-        <v>4.72</v>
+        <v>4.12</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>5010</v>
+        <v>241000</v>
       </c>
       <c r="K10" t="n">
-        <v>5120</v>
+        <v>253000</v>
       </c>
       <c r="L10" t="n">
-        <v>5990</v>
+        <v>257000</v>
       </c>
       <c r="M10" t="n">
-        <v>4950</v>
+        <v>233500</v>
       </c>
       <c r="N10" t="n">
-        <v>1.4</v>
+        <v>4.08</v>
       </c>
       <c r="O10" t="n">
-        <v>235936129505</v>
+        <v>96681347250</v>
       </c>
       <c r="P10" t="n">
-        <v>8100</v>
+        <v>1233000</v>
       </c>
       <c r="Q10" t="n">
-        <v>592</v>
+        <v>120000</v>
       </c>
       <c r="R10" t="n">
-        <v>83000</v>
+        <v>-78000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 증시 상승 및 엠바고 해제된 2200억 규모 선주문 발주서 기반 상승 기대감. 주포의 빌드업 가능성 언급.</t>
+          <t>아일리아 및 경구용 인슐린 관련 기대감, 릴레이 계약 공시 예상. 외인 공매도 숏커버링 및 캐나다/독일/이탈리아 계약 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['미국증시', '선주문', '주포']</t>
+          <t>['아일리아', '경구용인슐린', '계약공시']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>246000</v>
+        <v>5140</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.07%</t>
+          <t>'+2.59%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.04</v>
+        <v>3.32</v>
       </c>
       <c r="E11" t="n">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="F11" t="n">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G11" t="n">
-        <v>1175</v>
+        <v>497</v>
       </c>
       <c r="H11" t="n">
-        <v>4.12</v>
+        <v>4.72</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>241000</v>
+        <v>5010</v>
       </c>
       <c r="K11" t="n">
-        <v>253000</v>
+        <v>5120</v>
       </c>
       <c r="L11" t="n">
-        <v>257000</v>
+        <v>5990</v>
       </c>
       <c r="M11" t="n">
-        <v>233500</v>
+        <v>4950</v>
       </c>
       <c r="N11" t="n">
-        <v>4.08</v>
+        <v>1.4</v>
       </c>
       <c r="O11" t="n">
-        <v>94050829250</v>
+        <v>237101050545</v>
       </c>
       <c r="P11" t="n">
-        <v>1233000</v>
+        <v>8100</v>
       </c>
       <c r="Q11" t="n">
-        <v>120000</v>
+        <v>592</v>
       </c>
       <c r="R11" t="n">
-        <v>-78000</v>
+        <v>83000</v>
       </c>
       <c r="S11" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>아일리아 및 경구용 인슐린 관련 기대감, 릴레이 계약 공시 예상. 외인 공매도 숏커버링 및 캐나다/독일/이탈리아 계약 기대.</t>
+          <t>미국 증시 호조 속 빛과전자 상승세. 2200억 규모 선주문 발주서 내용 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['아일리아', '경구용인슐린', '계약공시']</t>
+          <t>['선주문', '발주서', '미국증시']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,191 +1476,191 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>271250</v>
+        <v>6960</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.28%</t>
+          <t>'-0.29%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.04</v>
+        <v>-0.77</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>90</v>
       </c>
       <c r="F12" t="n">
-        <v>486</v>
+        <v>57</v>
       </c>
       <c r="G12" t="n">
-        <v>1310</v>
+        <v>225</v>
       </c>
       <c r="H12" t="n">
-        <v>46.37</v>
+        <v>1.1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>272000</v>
+        <v>6980</v>
       </c>
       <c r="K12" t="n">
-        <v>269500</v>
+        <v>7000</v>
       </c>
       <c r="L12" t="n">
-        <v>279500</v>
+        <v>7240</v>
       </c>
       <c r="M12" t="n">
-        <v>268500</v>
+        <v>6580</v>
       </c>
       <c r="N12" t="n">
-        <v>46.41</v>
+        <v>1.87</v>
       </c>
       <c r="O12" t="n">
-        <v>3487864522250</v>
+        <v>69213100105</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>11370</v>
       </c>
       <c r="Q12" t="n">
-        <v>90200</v>
+        <v>3300</v>
       </c>
       <c r="R12" t="n">
-        <v>1548000</v>
+        <v>20000</v>
       </c>
       <c r="S12" t="n">
-        <v>-319000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 언급과 함께 외인/국군 매도세 언급. 실적 110조 이상 예상에도 불구하고 상승 여력 제한적 관망.</t>
+          <t>보안주로 분류되며 금융권 공략 뉴스 부각. 라온시큐어와의 비교 언급 및 거래량 대비 주가 움직임에 대한 아쉬움 표출.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['실적', '매도세', '정치']</t>
+          <t>['보안', '금융권']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12890</v>
+        <v>270500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.92%</t>
+          <t>'-0.55%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.88</v>
+        <v>-0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>88</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>65</v>
+        <v>498</v>
       </c>
       <c r="G13" t="n">
-        <v>240</v>
+        <v>1279</v>
       </c>
       <c r="H13" t="n">
-        <v>1.42</v>
+        <v>46.37</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13010</v>
+        <v>272000</v>
       </c>
       <c r="K13" t="n">
-        <v>12330</v>
+        <v>269500</v>
       </c>
       <c r="L13" t="n">
-        <v>13560</v>
+        <v>279500</v>
       </c>
       <c r="M13" t="n">
-        <v>12220</v>
+        <v>268500</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>46.41</v>
       </c>
       <c r="O13" t="n">
-        <v>48063563280</v>
+        <v>3592667058750</v>
       </c>
       <c r="P13" t="n">
-        <v>22250</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>6000</v>
+        <v>90200</v>
       </c>
       <c r="R13" t="n">
-        <v>-152000</v>
+        <v>1548000</v>
       </c>
       <c r="S13" t="n">
-        <v>16000</v>
+        <v>-319000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
+          <t>외인·국장 매도세 지속 속 삼전 실적 110조 이상 전망. AMD CEO 방한 HBM 주문 및 파운드리 계약 소식.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['유증', '신주상장', '자사주매집']</t>
+          <t>['HBM', '파운드리', '실적']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>80700</v>
+        <v>80600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.98%</t>
+          <t>'-1.10%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F14" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G14" t="n">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="H14" t="n">
         <v>22.59</v>
@@ -1714,7 +1714,7 @@
         <v>22.56</v>
       </c>
       <c r="O14" t="n">
-        <v>157851366700</v>
+        <v>159958286200</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17490</v>
+        <v>17430</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.46%</t>
+          <t>'-1.80%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.11</v>
       </c>
       <c r="E15" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F15" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G15" t="n">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="H15" t="n">
         <v>9.5</v>
@@ -1806,7 +1806,7 @@
         <v>9.390000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>53059059280</v>
+        <v>54242767410</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6850</v>
+        <v>12760</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.86%</t>
+          <t>'-1.92%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.77</v>
+        <v>1.88</v>
       </c>
       <c r="E16" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F16" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="G16" t="n">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6980</v>
+        <v>13010</v>
       </c>
       <c r="K16" t="n">
-        <v>7000</v>
+        <v>12330</v>
       </c>
       <c r="L16" t="n">
-        <v>7240</v>
+        <v>13560</v>
       </c>
       <c r="M16" t="n">
-        <v>6580</v>
+        <v>12220</v>
       </c>
       <c r="N16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>67986837510</v>
+        <v>48621490520</v>
       </c>
       <c r="P16" t="n">
-        <v>11370</v>
+        <v>22250</v>
       </c>
       <c r="Q16" t="n">
-        <v>3300</v>
+        <v>6000</v>
       </c>
       <c r="R16" t="n">
-        <v>20000</v>
+        <v>-152000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>보안주로 분류되며 금융권 공략 뉴스 부각. 라온시큐어와의 비교 언급 및 거래량 대비 주가 움직임에 대한 아쉬움 표출.</t>
+          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['보안', '금융권']</t>
+          <t>['유증', '신주상장', '자사주매집']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13080</v>
+        <v>1729000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.32%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>24</v>
+        <v>448</v>
       </c>
       <c r="G17" t="n">
-        <v>86</v>
+        <v>1922</v>
       </c>
       <c r="H17" t="n">
-        <v>3.18</v>
+        <v>49.71</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,91 +1975,91 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13390</v>
+        <v>1773000</v>
       </c>
       <c r="K17" t="n">
-        <v>13770</v>
+        <v>1728000</v>
       </c>
       <c r="L17" t="n">
-        <v>13830</v>
+        <v>1779000</v>
       </c>
       <c r="M17" t="n">
-        <v>13070</v>
+        <v>1725000</v>
       </c>
       <c r="N17" t="n">
-        <v>3.12</v>
+        <v>49.76</v>
       </c>
       <c r="O17" t="n">
-        <v>26770698045</v>
+        <v>3578950161500</v>
       </c>
       <c r="P17" t="n">
-        <v>20300</v>
+        <v>2987000</v>
       </c>
       <c r="Q17" t="n">
-        <v>3020</v>
+        <v>403000</v>
       </c>
       <c r="R17" t="n">
-        <v>-313000</v>
+        <v>-471000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-89000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
+          <t>외인 매도세 지속 및 추세선 하향 돌파. 하이닉스 향후 전망에 대한 부정적 의견 대두.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['전선주', '박스권', '공매도']</t>
+          <t>['외인매도', '추세선', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1729000</v>
+        <v>13050</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.48%</t>
+          <t>'-2.54%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>800</v>
+        <v>53</v>
       </c>
       <c r="F18" t="n">
-        <v>441</v>
+        <v>24</v>
       </c>
       <c r="G18" t="n">
-        <v>1943</v>
+        <v>86</v>
       </c>
       <c r="H18" t="n">
-        <v>49.71</v>
+        <v>3.18</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,60 +2067,60 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1773000</v>
+        <v>13390</v>
       </c>
       <c r="K18" t="n">
-        <v>1728000</v>
+        <v>13770</v>
       </c>
       <c r="L18" t="n">
-        <v>1779000</v>
+        <v>13830</v>
       </c>
       <c r="M18" t="n">
-        <v>1725000</v>
+        <v>13050</v>
       </c>
       <c r="N18" t="n">
-        <v>49.76</v>
+        <v>3.12</v>
       </c>
       <c r="O18" t="n">
-        <v>3483211659500</v>
+        <v>27061183885</v>
       </c>
       <c r="P18" t="n">
-        <v>2987000</v>
+        <v>20300</v>
       </c>
       <c r="Q18" t="n">
-        <v>403000</v>
+        <v>3020</v>
       </c>
       <c r="R18" t="n">
-        <v>-471000</v>
+        <v>-313000</v>
       </c>
       <c r="S18" t="n">
-        <v>-89000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>정치적 이슈와 함께 나스닥 및 외인 매도세로 인한 하락세 지속. 추세선 하향 돌파 및 공매도 관련 언급.</t>
+          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['정치', '매도세', '추세선']</t>
+          <t>['전선주', '박스권', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>46000</v>
+        <v>46100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.95%</t>
+          <t>'-2.74%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F19" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G19" t="n">
-        <v>2347</v>
+        <v>2353</v>
       </c>
       <c r="H19" t="n">
         <v>14.12</v>
@@ -2174,7 +2174,7 @@
         <v>14.1</v>
       </c>
       <c r="O19" t="n">
-        <v>42978287850</v>
+        <v>43415649100</v>
       </c>
       <c r="P19" t="n">
         <v>69200</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17980</v>
+        <v>17900</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.97%</t>
+          <t>'-3.40%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1.11</v>
       </c>
       <c r="E20" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F20" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G20" t="n">
-        <v>1114</v>
+        <v>1131</v>
       </c>
       <c r="H20" t="n">
         <v>4.92</v>
@@ -2266,7 +2266,7 @@
         <v>3.81</v>
       </c>
       <c r="O20" t="n">
-        <v>283729352470</v>
+        <v>284719902745</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30150</v>
+        <v>30050</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.04%</t>
+          <t>'-5.35%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F21" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G21" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="H21" t="n">
         <v>10.78</v>
@@ -2358,7 +2358,7 @@
         <v>10.77</v>
       </c>
       <c r="O21" t="n">
-        <v>101521691000</v>
+        <v>102632223525</v>
       </c>
       <c r="P21" t="n">
         <v>75900</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>가온전선과 비교되며 실력 및 기술력 차이 부각. 개인 매수세와 외인 매도세 관찰.</t>
+          <t>가온전선과의 비교 속 대한전선 급락세 지속. 외인 매도 물량 출회.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['비교', '매도세', '개인']</t>
+          <t>['급락', '외인매도', '가온전선']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12700</v>
+        <v>12630</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.43%</t>
+          <t>'-7.94%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2424,7 +2424,7 @@
         <v>69</v>
       </c>
       <c r="G22" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H22" t="n">
         <v>2.04</v>
@@ -2450,7 +2450,7 @@
         <v>2.47</v>
       </c>
       <c r="O22" t="n">
-        <v>59510499040</v>
+        <v>59719984205</v>
       </c>
       <c r="P22" t="n">
         <v>39600</v>

--- a/data/trending_integrated_20261007_14.xlsx
+++ b/data/trending_integrated_20261007_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H2" t="n">
         <v>3.27</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26384852214</v>
+        <v>26387993084</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>국전</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2765</v>
+        <v>6960</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.45%</t>
+          <t>'+22.32%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.05</v>
+        <v>-0.77</v>
       </c>
       <c r="E3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F3" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G3" t="n">
-        <v>103</v>
+        <v>226</v>
       </c>
       <c r="H3" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2395</v>
+        <v>5690</v>
       </c>
       <c r="K3" t="n">
-        <v>2410</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>3020</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2405</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.31</v>
+        <v>1.87</v>
       </c>
       <c r="O3" t="n">
-        <v>40435415416</v>
+        <v>70147000000</v>
       </c>
       <c r="P3" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-120000</v>
+        <v>20000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>흑사병 테마 관련주로 언급되며 거래량은 터졌으나 큰 상승은 못함. 반도체/이차전지 소재 업체로 변신 시도 언급.</t>
+          <t>보안주로 분류되며 금융권 공략 뉴스 부각. 라온시큐어와의 비교 언급 및 거래량 대비 주가 움직임에 대한 아쉬움 표출.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['흑사병', '테마주']</t>
+          <t>['보안', '금융권']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>307750</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11080</v>
+        <v>11180</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.58%</t>
+          <t>'+15.62%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.17</v>
       </c>
       <c r="E4" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F4" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G4" t="n">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="H4" t="n">
         <v>5.01</v>
@@ -785,7 +785,7 @@
         <v>11020</v>
       </c>
       <c r="L4" t="n">
-        <v>11240</v>
+        <v>11250</v>
       </c>
       <c r="M4" t="n">
         <v>10300</v>
@@ -794,7 +794,7 @@
         <v>4.84</v>
       </c>
       <c r="O4" t="n">
-        <v>27725474380</v>
+        <v>29259498240</v>
       </c>
       <c r="P4" t="n">
         <v>15900</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>러시아 흑사병·케냐 에볼라 발병 소식에 신풍제약 급등. 만능 테마주로서의 기대감 부각.</t>
+          <t>흑사병 및 기타 전염병 확산 관련 뉴스로 인한 테마주 부각. 모건스탠리 등의 매수세 유입이 언급됨.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['흑사병', '에볼라', '테마주']</t>
+          <t>['흑사병', '테마주', '전염병']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>국전</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7730</v>
+        <v>2765</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.52%</t>
+          <t>'+15.45%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>154</v>
+        <v>92</v>
       </c>
       <c r="F5" t="n">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
-        <v>510</v>
+        <v>110</v>
       </c>
       <c r="H5" t="n">
-        <v>5.12</v>
+        <v>1.36</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6750</v>
+        <v>2395</v>
       </c>
       <c r="K5" t="n">
-        <v>6710</v>
+        <v>2410</v>
       </c>
       <c r="L5" t="n">
-        <v>8450</v>
+        <v>3020</v>
       </c>
       <c r="M5" t="n">
-        <v>6690</v>
+        <v>2405</v>
       </c>
       <c r="N5" t="n">
-        <v>5.14</v>
+        <v>1.31</v>
       </c>
       <c r="O5" t="n">
-        <v>138229200460</v>
+        <v>40679729966</v>
       </c>
       <c r="P5" t="n">
-        <v>23500</v>
+        <v>6000</v>
       </c>
       <c r="Q5" t="n">
-        <v>2890</v>
+        <v>1700</v>
       </c>
       <c r="R5" t="n">
-        <v>-631000</v>
+        <v>-120000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정부의 용적률 상향 및 그린벨트 해제 발표와 함께 성수동 삼표타워 건설 시작. 만원 돌파 기대감 및 거래량 증가.</t>
+          <t>흑사병 테마 관련주로 언급되며 거래량은 터졌으나 큰 상승은 못함. 반도체/이차전지 소재 업체로 변신 시도 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['용적률', '그린벨트', '거래량']</t>
+          <t>['흑사병', '테마주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,43 +919,43 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>307750</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16820</v>
+        <v>7740</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+13.11%</t>
+          <t>'+14.67%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.98</v>
+        <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="F6" t="n">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="G6" t="n">
-        <v>335</v>
+        <v>516</v>
       </c>
       <c r="H6" t="n">
-        <v>2.37</v>
+        <v>5.12</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14870</v>
+        <v>6750</v>
       </c>
       <c r="K6" t="n">
-        <v>15480</v>
+        <v>6710</v>
       </c>
       <c r="L6" t="n">
-        <v>17590</v>
+        <v>8450</v>
       </c>
       <c r="M6" t="n">
-        <v>14600</v>
+        <v>6690</v>
       </c>
       <c r="N6" t="n">
-        <v>1.39</v>
+        <v>5.14</v>
       </c>
       <c r="O6" t="n">
-        <v>287351802440</v>
+        <v>139389364000</v>
       </c>
       <c r="P6" t="n">
-        <v>17590</v>
+        <v>23500</v>
       </c>
       <c r="Q6" t="n">
-        <v>6320</v>
+        <v>2890</v>
       </c>
       <c r="R6" t="n">
-        <v>-95000</v>
+        <v>-631000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>국내외 해킹·보안 이슈 부각 속 라온시큐어 상승. 농협·KDB생명 해킹 방어 및 양자보안 공급 논의.</t>
+          <t>정부의 용적률 상향 및 그린벨트 해제 발표와 함께 성수동 삼표타워 건설 시작. 만원 돌파 기대감 및 거래량 증가.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['양자보안', '해킹', '보안주']</t>
+          <t>['용적률', '그린벨트', '거래량']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25950</v>
+        <v>16790</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+13.07%</t>
+          <t>'+12.91%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.4</v>
+        <v>0.98</v>
       </c>
       <c r="E7" t="n">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>116</v>
       </c>
       <c r="G7" t="n">
-        <v>288</v>
+        <v>339</v>
       </c>
       <c r="H7" t="n">
-        <v>2.82</v>
+        <v>2.37</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>22950</v>
+        <v>14870</v>
       </c>
       <c r="K7" t="n">
-        <v>26200</v>
+        <v>15480</v>
       </c>
       <c r="L7" t="n">
-        <v>27600</v>
+        <v>17590</v>
       </c>
       <c r="M7" t="n">
-        <v>25550</v>
+        <v>14600</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>1.39</v>
       </c>
       <c r="O7" t="n">
-        <v>102310983300</v>
+        <v>289235553370</v>
       </c>
       <c r="P7" t="n">
-        <v>30100</v>
+        <v>17590</v>
       </c>
       <c r="Q7" t="n">
-        <v>11140</v>
+        <v>6320</v>
       </c>
       <c r="R7" t="n">
-        <v>160000</v>
+        <v>-95000</v>
       </c>
       <c r="S7" t="n">
-        <v>-227000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>유리 기술력 기반 성장 기대감. 브로드컴, 씨게이트 등 대기업과의 협력 가능성.</t>
+          <t>국내외 해킹·보안 이슈 부각 속 라온시큐어 상승. 농협·KDB생명 해킹 방어 및 양자보안 공급 논의.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유리', '기술력', '협력']</t>
+          <t>['양자보안', '해킹', '보안주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,43 +1103,43 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2635</v>
+        <v>25850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+10.48%</t>
+          <t>'+12.64%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.29</v>
+        <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>89</v>
+        <v>289</v>
       </c>
       <c r="H8" t="n">
-        <v>0.82</v>
+        <v>2.82</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2385</v>
+        <v>22950</v>
       </c>
       <c r="K8" t="n">
-        <v>2510</v>
+        <v>26200</v>
       </c>
       <c r="L8" t="n">
-        <v>2900</v>
+        <v>27600</v>
       </c>
       <c r="M8" t="n">
-        <v>2505</v>
+        <v>25550</v>
       </c>
       <c r="N8" t="n">
-        <v>1.11</v>
+        <v>2.42</v>
       </c>
       <c r="O8" t="n">
-        <v>14986116415</v>
+        <v>102827820675</v>
       </c>
       <c r="P8" t="n">
-        <v>4760</v>
+        <v>30100</v>
       </c>
       <c r="Q8" t="n">
-        <v>973</v>
+        <v>11140</v>
       </c>
       <c r="R8" t="n">
-        <v>45000</v>
+        <v>160000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-227000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
+          <t>유리 기술력 기반 성장 기대감. 브로드컴, 씨게이트 등 대기업과의 협력 가능성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['바이오', '유상증자', '기술적 반등']</t>
+          <t>['유리', '기술력', '협력']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>204270</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13620</v>
+        <v>13700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+10.46%</t>
+          <t>'+11.11%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F9" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G9" t="n">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="H9" t="n">
         <v>0.79</v>
@@ -1254,7 +1254,7 @@
         <v>0.48</v>
       </c>
       <c r="O9" t="n">
-        <v>214458798545</v>
+        <v>218308679585</v>
       </c>
       <c r="P9" t="n">
         <v>20850</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>가스터빈 블레이드 첫 납품 뉴스 확인. 불확실성 해소 및 원전 투자 기대감.</t>
+          <t>한화파워향 가스터빈 블레이드 첫 납품 관련 공시 및 원전 사업 진출 가능성 언급. 일부 부정적 전망도 존재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['납품', '가스터빈', '원전']</t>
+          <t>['가스터빈', '블레이드', '납품']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>248500</v>
+        <v>2645</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.11%</t>
+          <t>'+10.90%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.04</v>
+        <v>-0.29</v>
       </c>
       <c r="E10" t="n">
-        <v>206</v>
+        <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="G10" t="n">
-        <v>1188</v>
+        <v>91</v>
       </c>
       <c r="H10" t="n">
-        <v>4.12</v>
+        <v>0.82</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,47 +1331,47 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>241000</v>
+        <v>2385</v>
       </c>
       <c r="K10" t="n">
-        <v>253000</v>
+        <v>2510</v>
       </c>
       <c r="L10" t="n">
-        <v>257000</v>
+        <v>2900</v>
       </c>
       <c r="M10" t="n">
-        <v>233500</v>
+        <v>2505</v>
       </c>
       <c r="N10" t="n">
-        <v>4.08</v>
+        <v>1.11</v>
       </c>
       <c r="O10" t="n">
-        <v>96681347250</v>
+        <v>15211879880</v>
       </c>
       <c r="P10" t="n">
-        <v>1233000</v>
+        <v>4760</v>
       </c>
       <c r="Q10" t="n">
-        <v>120000</v>
+        <v>973</v>
       </c>
       <c r="R10" t="n">
-        <v>-78000</v>
+        <v>45000</v>
       </c>
       <c r="S10" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>아일리아 및 경구용 인슐린 관련 기대감, 릴레이 계약 공시 예상. 외인 공매도 숏커버링 및 캐나다/독일/이탈리아 계약 기대.</t>
+          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['아일리아', '경구용인슐린', '계약공시']</t>
+          <t>['바이오', '유상증자', '기술적 반등']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5140</v>
+        <v>5220</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.59%</t>
+          <t>'+4.19%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>223</v>
       </c>
       <c r="F11" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G11" t="n">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="H11" t="n">
         <v>4.72</v>
@@ -1438,7 +1438,7 @@
         <v>1.4</v>
       </c>
       <c r="O11" t="n">
-        <v>237101050545</v>
+        <v>239512941495</v>
       </c>
       <c r="P11" t="n">
         <v>8100</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 증시 호조 속 빛과전자 상승세. 2200억 규모 선주문 발주서 내용 언급.</t>
+          <t>미국 증시 강세 및 2200억원 규모 선주문 관련 언급이 있으나, 투자자들의 불안감도 공존함.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['선주문', '발주서', '미국증시']</t>
+          <t>['선주문', '미국 증시', '물량']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6960</v>
+        <v>247000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.29%</t>
+          <t>'+2.49%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.77</v>
+        <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>90</v>
+        <v>216</v>
       </c>
       <c r="F12" t="n">
-        <v>57</v>
+        <v>128</v>
       </c>
       <c r="G12" t="n">
-        <v>225</v>
+        <v>1205</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1</v>
+        <v>4.12</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,60 +1515,60 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>6980</v>
+        <v>241000</v>
       </c>
       <c r="K12" t="n">
-        <v>7000</v>
+        <v>253000</v>
       </c>
       <c r="L12" t="n">
-        <v>7240</v>
+        <v>257000</v>
       </c>
       <c r="M12" t="n">
-        <v>6580</v>
+        <v>233500</v>
       </c>
       <c r="N12" t="n">
-        <v>1.87</v>
+        <v>4.08</v>
       </c>
       <c r="O12" t="n">
-        <v>69213100105</v>
+        <v>100438413500</v>
       </c>
       <c r="P12" t="n">
-        <v>11370</v>
+        <v>1233000</v>
       </c>
       <c r="Q12" t="n">
-        <v>3300</v>
+        <v>120000</v>
       </c>
       <c r="R12" t="n">
-        <v>20000</v>
+        <v>-78000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>보안주로 분류되며 금융권 공략 뉴스 부각. 라온시큐어와의 비교 언급 및 거래량 대비 주가 움직임에 대한 아쉬움 표출.</t>
+          <t>아일리아 관련 기대감과 함께 경구용 인슐린 10조원대 L/O 예상, 캐나다 및 독일 계약 공시 가능성이 언급됨.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['보안', '금융권']</t>
+          <t>['아일리아', '경구용 인슐린', '계약 공시']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="G13" t="n">
-        <v>1279</v>
+        <v>1241</v>
       </c>
       <c r="H13" t="n">
         <v>46.37</v>
@@ -1622,7 +1622,7 @@
         <v>46.41</v>
       </c>
       <c r="O13" t="n">
-        <v>3592667058750</v>
+        <v>3672152443750</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외인·국장 매도세 지속 속 삼전 실적 110조 이상 전망. AMD CEO 방한 HBM 주문 및 파운드리 계약 소식.</t>
+          <t>AMD CEO의 HBM 대량 주문 및 파운드리 계약 관련 뉴스가 있으나, 정치적 언급과 부정적 전망이 혼재됨.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>80600</v>
+        <v>80700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.10%</t>
+          <t>'-0.98%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F14" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G14" t="n">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="H14" t="n">
         <v>22.59</v>
@@ -1714,7 +1714,7 @@
         <v>22.56</v>
       </c>
       <c r="O14" t="n">
-        <v>159958286200</v>
+        <v>162199872400</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1759,70 +1759,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17430</v>
+        <v>12820</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.80%</t>
+          <t>'-1.46%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.11</v>
+        <v>1.88</v>
       </c>
       <c r="E15" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F15" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="G15" t="n">
-        <v>422</v>
+        <v>244</v>
       </c>
       <c r="H15" t="n">
-        <v>9.5</v>
+        <v>1.42</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17750</v>
+        <v>13010</v>
       </c>
       <c r="K15" t="n">
-        <v>17970</v>
+        <v>12330</v>
       </c>
       <c r="L15" t="n">
-        <v>18030</v>
+        <v>13560</v>
       </c>
       <c r="M15" t="n">
-        <v>17420</v>
+        <v>12220</v>
       </c>
       <c r="N15" t="n">
-        <v>9.390000000000001</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>54242767410</v>
+        <v>48974905750</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>22250</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>6000</v>
       </c>
       <c r="R15" t="n">
-        <v>-31000</v>
+        <v>-152000</v>
       </c>
       <c r="S15" t="n">
-        <v>-50000</v>
+        <v>16000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 원전 건설 호재 및 수주 목표 달성 기대감. 주주 호소 및 긍정적 전망 다수.</t>
+          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전', '수주', '주주']</t>
+          <t>['유증', '신주상장', '자사주매집']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12760</v>
+        <v>17430</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.92%</t>
+          <t>'-1.80%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.88</v>
+        <v>0.11</v>
       </c>
       <c r="E16" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="G16" t="n">
-        <v>244</v>
+        <v>431</v>
       </c>
       <c r="H16" t="n">
-        <v>1.42</v>
+        <v>9.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13010</v>
+        <v>17750</v>
       </c>
       <c r="K16" t="n">
-        <v>12330</v>
+        <v>17970</v>
       </c>
       <c r="L16" t="n">
-        <v>13560</v>
+        <v>18030</v>
       </c>
       <c r="M16" t="n">
-        <v>12220</v>
+        <v>17420</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>48621490520</v>
+        <v>55260139285</v>
       </c>
       <c r="P16" t="n">
-        <v>22250</v>
+        <v>40350</v>
       </c>
       <c r="Q16" t="n">
-        <v>6000</v>
+        <v>3320</v>
       </c>
       <c r="R16" t="n">
-        <v>-152000</v>
+        <v>-31000</v>
       </c>
       <c r="S16" t="n">
-        <v>16000</v>
+        <v>-50000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
+          <t>미국 원전 건설 호재 및 수주 목표 달성 기대감. 주주 호소 및 긍정적 전망 다수.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['유증', '신주상장', '자사주매집']</t>
+          <t>['원전', '수주', '주주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1729000</v>
+        <v>46350</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.48%</t>
+          <t>'-2.22%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>800</v>
+        <v>375</v>
       </c>
       <c r="F17" t="n">
-        <v>448</v>
+        <v>206</v>
       </c>
       <c r="G17" t="n">
-        <v>1922</v>
+        <v>2364</v>
       </c>
       <c r="H17" t="n">
-        <v>49.71</v>
+        <v>14.12</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1773000</v>
+        <v>47400</v>
       </c>
       <c r="K17" t="n">
-        <v>1728000</v>
+        <v>46350</v>
       </c>
       <c r="L17" t="n">
-        <v>1779000</v>
+        <v>47850</v>
       </c>
       <c r="M17" t="n">
-        <v>1725000</v>
+        <v>45450</v>
       </c>
       <c r="N17" t="n">
-        <v>49.76</v>
+        <v>14.1</v>
       </c>
       <c r="O17" t="n">
-        <v>3578950161500</v>
+        <v>44334718800</v>
       </c>
       <c r="P17" t="n">
-        <v>2987000</v>
+        <v>69200</v>
       </c>
       <c r="Q17" t="n">
-        <v>403000</v>
+        <v>24150</v>
       </c>
       <c r="R17" t="n">
-        <v>-471000</v>
+        <v>-61000</v>
       </c>
       <c r="S17" t="n">
-        <v>-89000</v>
+        <v>2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>외인 매도세 지속 및 추세선 하향 돌파. 하이닉스 향후 전망에 대한 부정적 의견 대두.</t>
+          <t>FDA 승인 가능성 90% 이상 전망 및 2~3조원 매출 기대감. 공매도와의 공방 속 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['외인매도', '추세선', '공매도']</t>
+          <t>['FDA', '간암', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13050</v>
+        <v>1729500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.54%</t>
+          <t>'-2.45%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>24</v>
+        <v>441</v>
       </c>
       <c r="G18" t="n">
-        <v>86</v>
+        <v>1909</v>
       </c>
       <c r="H18" t="n">
-        <v>3.18</v>
+        <v>49.71</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,152 +2067,152 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13390</v>
+        <v>1773000</v>
       </c>
       <c r="K18" t="n">
-        <v>13770</v>
+        <v>1728000</v>
       </c>
       <c r="L18" t="n">
-        <v>13830</v>
+        <v>1779000</v>
       </c>
       <c r="M18" t="n">
-        <v>13050</v>
+        <v>1725000</v>
       </c>
       <c r="N18" t="n">
-        <v>3.12</v>
+        <v>49.76</v>
       </c>
       <c r="O18" t="n">
-        <v>27061183885</v>
+        <v>3663042220000</v>
       </c>
       <c r="P18" t="n">
-        <v>20300</v>
+        <v>2987000</v>
       </c>
       <c r="Q18" t="n">
-        <v>3020</v>
+        <v>403000</v>
       </c>
       <c r="R18" t="n">
-        <v>-313000</v>
+        <v>-471000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-89000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
+          <t>외국인 매도세와 추세선 하향 돌파에 대한 부정적 전망이 지배적. 정치적 요인도 언급됨.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['전선주', '박스권', '공매도']</t>
+          <t>['외국인', '추세선', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>46100</v>
+        <v>13020</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.74%</t>
+          <t>'-2.76%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>373</v>
+        <v>53</v>
       </c>
       <c r="F19" t="n">
-        <v>206</v>
+        <v>24</v>
       </c>
       <c r="G19" t="n">
-        <v>2353</v>
+        <v>86</v>
       </c>
       <c r="H19" t="n">
-        <v>14.12</v>
+        <v>3.18</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>47400</v>
+        <v>13390</v>
       </c>
       <c r="K19" t="n">
-        <v>46350</v>
+        <v>13770</v>
       </c>
       <c r="L19" t="n">
-        <v>47850</v>
+        <v>13830</v>
       </c>
       <c r="M19" t="n">
-        <v>45450</v>
+        <v>13010</v>
       </c>
       <c r="N19" t="n">
-        <v>14.1</v>
+        <v>3.12</v>
       </c>
       <c r="O19" t="n">
-        <v>43415649100</v>
+        <v>27417784645</v>
       </c>
       <c r="P19" t="n">
-        <v>69200</v>
+        <v>20300</v>
       </c>
       <c r="Q19" t="n">
-        <v>24150</v>
+        <v>3020</v>
       </c>
       <c r="R19" t="n">
-        <v>-61000</v>
+        <v>-313000</v>
       </c>
       <c r="S19" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>FDA 승인 가능성 90% 이상 전망 및 2~3조원 매출 기대감. 공매도와의 공방 속 주가 상승 기대.</t>
+          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['FDA', '간암', '공매도']</t>
+          <t>['전선주', '박스권', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
@@ -2234,13 +2234,13 @@
         <v>1.11</v>
       </c>
       <c r="E20" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F20" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G20" t="n">
-        <v>1131</v>
+        <v>1150</v>
       </c>
       <c r="H20" t="n">
         <v>4.92</v>
@@ -2260,13 +2260,13 @@
         <v>19870</v>
       </c>
       <c r="M20" t="n">
-        <v>17855</v>
+        <v>17850</v>
       </c>
       <c r="N20" t="n">
         <v>3.81</v>
       </c>
       <c r="O20" t="n">
-        <v>284719902745</v>
+        <v>286531021200</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30050</v>
+        <v>30100</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.35%</t>
+          <t>'-5.20%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F21" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G21" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="H21" t="n">
         <v>10.78</v>
@@ -2358,7 +2358,7 @@
         <v>10.77</v>
       </c>
       <c r="O21" t="n">
-        <v>102632223525</v>
+        <v>103581748400</v>
       </c>
       <c r="P21" t="n">
         <v>75900</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12630</v>
+        <v>12590</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.94%</t>
+          <t>'-8.24%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.43</v>
       </c>
       <c r="E22" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F22" t="n">
         <v>69</v>
       </c>
       <c r="G22" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H22" t="n">
         <v>2.04</v>
@@ -2450,7 +2450,7 @@
         <v>2.47</v>
       </c>
       <c r="O22" t="n">
-        <v>59719984205</v>
+        <v>60142254085</v>
       </c>
       <c r="P22" t="n">
         <v>39600</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>누리호 발사 성공에도 불구하고 재료 소멸 및 급락. 주포 이탈 가능성 언급.</t>
+          <t>우주 항공 테마 부각 후 급락. 누리호 발사 성공 및 재료 소멸에 대한 언급이 있으며, 공매도 관련 논쟁도 있음.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['누리호', '재료소멸', '급락']</t>
+          <t>['우주항공', '재료소멸', '공매도']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
